--- a/docs/dailyreview/04_数据与事实/HT+华泰证券/FY2026/20260209-华泰证券-研究所行业周度观点及推荐.xlsx
+++ b/docs/dailyreview/04_数据与事实/HT+华泰证券/FY2026/20260209-华泰证券-研究所行业周度观点及推荐.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2026PythonWorld\warrenluccie.github.io\docs\dailyreview\04_数据与事实\HT+华泰证券\FY2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\warrenpyquant\examples\warrenluccie.github.io\docs\dailyreview\04_数据与事实\HT+华泰证券\FY2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596C33B3-A997-401C-B767-BE84FB8C7104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88BC6BA-3455-4C40-A52A-C7E0170E6480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="708">
   <si>
     <t>华泰研究所行业周度观点及推荐</t>
   </si>
@@ -1029,17 +1029,6 @@
     <t>14.1</t>
   </si>
   <si>
-    <t>战略配置窗口期开启
-金银
-金银本次回调主要由监管强化、美元短期走强等脉冲性因素引发，属波动放大而非中期顶部；从调整幅度看，金银跌幅已接近历史极端水平，调整或近尾声。以往历史是转加息，价格见顶；当前处于流动性宽松与经济复苏初期，黄金定价核心已转向美元信用弱化驱动的长期资产再配置，其在金融资产中占比仍低（约3.8%，有望增至5%），金价长期将呈震荡上行趋势。
-铜铝
-本轮强监管引发的去杠杆负反馈或接近尾声。工业金属大幅度下杀过程中触发了下游积极的补采，对价格形成了有效支撑。且部分家电品牌开始涨价传导压力。中下游环节部分企业已经提前放假，短期累库，价格预期震荡整固。铜、铝价格支撑位或在10万和2.3万。
-碳酸锂
-近期累库，短期供需双弱偏平衡。汽车行业压力犹存。价格回落至13万左右，行业反馈补库意愿强烈，或形成强支撑。
-板块估值
-1.2万铜价、2.3万铝价、13万锂价、1000元/克金价，很多个股估值处于8-12x的区间内。春节后若开工、积压订单补采和松流动性共振，或形成更为顺畅的上涨；金价预期升回$5000以上，铜铝价格或冲击1.5万美元和2.5万人民币，碳酸锂或在13-15万高位震荡。低估值且仍然可期的价格上涨，当前或是再次战略配置的难得窗口期。</t>
-  </si>
-  <si>
     <t>降息</t>
   </si>
   <si>
@@ -1055,22 +1044,13 @@
     <t>1.0万亿港元</t>
   </si>
   <si>
-    <t>随金、铜价格上涨，上修业绩。</t>
-  </si>
-  <si>
     <t>68.9%</t>
   </si>
   <si>
-    <t>807.7</t>
-  </si>
-  <si>
     <t>995.0</t>
   </si>
   <si>
     <t>56.7%</t>
-  </si>
-  <si>
-    <t>23.2%</t>
   </si>
   <si>
     <t>12.1</t>
@@ -3001,17 +2981,49 @@
     <t>PE</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
+  <si>
+    <t>战略配置窗口期开启
+金银
+金银本次回调主要由监管强化、美元短期走强等脉冲性因素引发，属波动放大而非中期顶部；从调整幅度看，金银跌幅已接近历史极端水平，调整或近尾声。以往历史是转加息，价格见顶；当前处于流动性宽松与经济复苏初期，黄金定价核心已转向美元信用弱化驱动的长期资产再配置，其在金融资产中占比仍低（约3.8%，有望增至5%），金价长期将呈震荡上行趋势。
+铜铝
+本轮强监管引发的去杠杆负反馈或接近尾声。工业金属大幅度下杀过程中触发了下游积极的补采，对价格形成了有效支撑。且部分家电品牌开始涨价传导压力。中下游环节部分企业已经提前放假，短期累库，价格预期震荡整固。铜、铝价格支撑位或在10万和2.3万。
+碳酸锂
+近期累库，短期供需双弱偏平衡。汽车行业压力犹存。价格回落至13万左右，行业反馈补库意愿强烈，或形成强支撑。
+板块估值
+1.2万铜价、2.3万铝价、13万锂价、1000元/克金价，很多个股估值处于8-12x的区间内。春节后若开工、积压订单补采和松流动性共振，或形成更为顺畅的上涨；金价预期升回$5000以上，铜铝价格或冲击1.5万美元和2.5万人民币，碳酸锂或在13-15万高位震荡。低估值且仍然可期的价格上涨，当前或是再次战略配置的难得窗口期。</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>随金、铜价格上涨，上修业绩。</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>归母净利润（亿元）</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026E</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027E</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>归母净利润增速</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="178" formatCode="0.0%"/>
-    <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="180" formatCode="0.0"/>
-    <numFmt numFmtId="181" formatCode="0.0_ "/>
-    <numFmt numFmtId="182" formatCode="#,##0.00_ ;@"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.0"/>
+    <numFmt numFmtId="179" formatCode="0.0_ "/>
+    <numFmt numFmtId="180" formatCode="#,##0.00_ ;@"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -3370,7 +3382,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="264">
+  <cellXfs count="266">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3681,7 +3693,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3696,10 +3708,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3729,7 +3741,7 @@
     <xf numFmtId="10" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3744,7 +3756,7 @@
     <xf numFmtId="9" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3762,7 +3774,7 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3774,7 +3786,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3807,19 +3819,19 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3828,7 +3840,7 @@
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3837,22 +3849,22 @@
     <xf numFmtId="9" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3861,7 +3873,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3885,10 +3897,10 @@
     <xf numFmtId="1" fontId="15" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="15" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3941,6 +3953,33 @@
     </xf>
     <xf numFmtId="49" fontId="15" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3965,181 +4004,160 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4437,24 +4455,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="200" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="193"/>
+      <c r="B1" s="201"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
+      <c r="E1" s="201"/>
+      <c r="F1" s="201"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="201"/>
+      <c r="I1" s="201"/>
+      <c r="J1" s="201"/>
+      <c r="K1" s="201"/>
+      <c r="L1" s="201"/>
+      <c r="M1" s="201"/>
+      <c r="N1" s="201"/>
+      <c r="O1" s="201"/>
+      <c r="P1" s="202"/>
       <c r="Q1" s="88"/>
       <c r="R1" s="88"/>
       <c r="S1" s="88"/>
@@ -4462,46 +4480,46 @@
       <c r="U1" s="88"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="204" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="197" t="s">
+      <c r="B2" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="198" t="s">
+      <c r="E2" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="195" t="s">
+      <c r="F2" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="197" t="s">
+      <c r="G2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="197" t="s">
+      <c r="H2" s="206" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="197" t="s">
+      <c r="I2" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="194" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="193"/>
-      <c r="L2" s="194" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="193"/>
-      <c r="N2" s="194" t="s">
-        <v>705</v>
-      </c>
-      <c r="O2" s="193"/>
-      <c r="P2" s="197" t="s">
+      <c r="J2" s="203" t="s">
+        <v>704</v>
+      </c>
+      <c r="K2" s="202"/>
+      <c r="L2" s="203" t="s">
+        <v>707</v>
+      </c>
+      <c r="M2" s="202"/>
+      <c r="N2" s="203" t="s">
+        <v>701</v>
+      </c>
+      <c r="O2" s="202"/>
+      <c r="P2" s="206" t="s">
         <v>13</v>
       </c>
       <c r="Q2" s="88"/>
@@ -4510,21 +4528,21 @@
       <c r="T2" s="88"/>
       <c r="U2" s="88"/>
     </row>
-    <row r="3" spans="1:21" ht="18" customHeight="1">
-      <c r="A3" s="196"/>
-      <c r="B3" s="196"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
+    <row r="3" spans="1:21" ht="14.25">
+      <c r="A3" s="205"/>
+      <c r="B3" s="205"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+      <c r="H3" s="208"/>
+      <c r="I3" s="208"/>
       <c r="J3" s="184" t="s">
-        <v>74</v>
+        <v>705</v>
       </c>
       <c r="K3" s="184" t="s">
-        <v>75</v>
+        <v>706</v>
       </c>
       <c r="L3" s="184" t="s">
         <v>74</v>
@@ -4538,7 +4556,7 @@
       <c r="O3" s="184" t="s">
         <v>75</v>
       </c>
-      <c r="P3" s="196"/>
+      <c r="P3" s="205"/>
       <c r="Q3" s="88"/>
       <c r="R3" s="88"/>
       <c r="S3" s="88"/>
@@ -4546,16 +4564,16 @@
       <c r="U3" s="88"/>
     </row>
     <row r="4" spans="1:21" ht="45">
-      <c r="A4" s="200" t="s">
-        <v>704</v>
-      </c>
-      <c r="B4" s="201" t="s">
+      <c r="A4" s="197" t="s">
+        <v>700</v>
+      </c>
+      <c r="B4" s="198" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="202" t="s">
+      <c r="C4" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="202" t="s">
+      <c r="D4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="E4" s="167" t="s">
@@ -4591,7 +4609,7 @@
       <c r="O4" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="P4" s="200" t="s">
+      <c r="P4" s="197" t="s">
         <v>79</v>
       </c>
       <c r="Q4" s="183"/>
@@ -4601,10 +4619,10 @@
       <c r="U4" s="88"/>
     </row>
     <row r="5" spans="1:21" ht="56.25">
-      <c r="A5" s="200"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="202"/>
+      <c r="A5" s="197"/>
+      <c r="B5" s="198"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
       <c r="E5" s="167" t="s">
         <v>91</v>
       </c>
@@ -4638,61 +4656,61 @@
       <c r="O5" s="170" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="200"/>
+      <c r="P5" s="197"/>
       <c r="Q5" s="183"/>
       <c r="R5" s="88"/>
       <c r="S5" s="88"/>
       <c r="T5" s="88"/>
       <c r="U5" s="88"/>
     </row>
-    <row r="6" spans="1:21" ht="315">
+    <row r="6" spans="1:21" ht="380.25" customHeight="1">
       <c r="A6" s="169" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="190" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="187" t="s">
+      <c r="C6" s="264" t="s">
+        <v>702</v>
+      </c>
+      <c r="D6" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="187" t="s">
-        <v>102</v>
-      </c>
       <c r="E6" s="181" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="175" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="175" t="s">
-        <v>105</v>
-      </c>
-      <c r="G6" s="179" t="s">
-        <v>106</v>
+      <c r="G6" s="265" t="s">
+        <v>703</v>
       </c>
       <c r="H6" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I6" s="177" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="175">
+        <v>807.7</v>
+      </c>
+      <c r="K6" s="175" t="s">
+        <v>106</v>
+      </c>
+      <c r="L6" s="173" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="175" t="s">
+      <c r="M6" s="173">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="N6" s="171" t="s">
         <v>108</v>
       </c>
-      <c r="K6" s="175" t="s">
+      <c r="O6" s="171" t="s">
         <v>109</v>
       </c>
-      <c r="L6" s="173" t="s">
-        <v>110</v>
-      </c>
-      <c r="M6" s="173" t="s">
-        <v>111</v>
-      </c>
-      <c r="N6" s="171" t="s">
-        <v>112</v>
-      </c>
-      <c r="O6" s="171" t="s">
-        <v>113</v>
-      </c>
       <c r="P6" s="169" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q6" s="183"/>
       <c r="R6" s="88"/>
@@ -4708,46 +4726,46 @@
         <v>76</v>
       </c>
       <c r="C7" s="186" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="186" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="180" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" s="174" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="178" t="s">
         <v>114</v>
-      </c>
-      <c r="D7" s="186" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="180" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" s="174" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" s="178" t="s">
-        <v>118</v>
       </c>
       <c r="H7" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I7" s="176" t="s">
+        <v>115</v>
+      </c>
+      <c r="J7" s="174" t="s">
+        <v>116</v>
+      </c>
+      <c r="K7" s="174" t="s">
+        <v>117</v>
+      </c>
+      <c r="L7" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="M7" s="172" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="174" t="s">
+      <c r="N7" s="170" t="s">
         <v>120</v>
       </c>
-      <c r="K7" s="174" t="s">
+      <c r="O7" s="170" t="s">
         <v>121</v>
       </c>
-      <c r="L7" s="172" t="s">
-        <v>122</v>
-      </c>
-      <c r="M7" s="172" t="s">
-        <v>123</v>
-      </c>
-      <c r="N7" s="170" t="s">
-        <v>124</v>
-      </c>
-      <c r="O7" s="170" t="s">
-        <v>125</v>
-      </c>
       <c r="P7" s="168" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q7" s="183"/>
       <c r="R7" s="88"/>
@@ -4756,44 +4774,44 @@
       <c r="U7" s="88"/>
     </row>
     <row r="8" spans="1:21" ht="22.5">
-      <c r="A8" s="203" t="s">
+      <c r="A8" s="191" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="204" t="s">
+      <c r="B8" s="192" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="193" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="181" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="205" t="s">
+      <c r="F8" s="175" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="205" t="s">
+      <c r="G8" s="179" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="181" t="s">
+      <c r="H8" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="177" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="175" t="s">
+      <c r="J8" s="175" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="179" t="s">
+      <c r="K8" s="175" t="s">
         <v>132</v>
       </c>
-      <c r="H8" s="175" t="s">
+      <c r="L8" s="173" t="s">
         <v>133</v>
       </c>
-      <c r="I8" s="177" t="s">
+      <c r="M8" s="173" t="s">
         <v>134</v>
-      </c>
-      <c r="J8" s="175" t="s">
-        <v>135</v>
-      </c>
-      <c r="K8" s="175" t="s">
-        <v>136</v>
-      </c>
-      <c r="L8" s="173" t="s">
-        <v>137</v>
-      </c>
-      <c r="M8" s="173" t="s">
-        <v>138</v>
       </c>
       <c r="N8" s="171" t="s">
         <v>100</v>
@@ -4801,8 +4819,8 @@
       <c r="O8" s="171" t="s">
         <v>100</v>
       </c>
-      <c r="P8" s="203" t="s">
-        <v>129</v>
+      <c r="P8" s="191" t="s">
+        <v>125</v>
       </c>
       <c r="Q8" s="183"/>
       <c r="R8" s="88"/>
@@ -4811,44 +4829,44 @@
       <c r="U8" s="88"/>
     </row>
     <row r="9" spans="1:21" ht="22.5">
-      <c r="A9" s="203"/>
-      <c r="B9" s="204"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="205"/>
+      <c r="A9" s="191"/>
+      <c r="B9" s="192"/>
+      <c r="C9" s="193"/>
+      <c r="D9" s="193"/>
       <c r="E9" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="175" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="179" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" s="177" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="175" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="175" t="s">
+      <c r="K9" s="175" t="s">
         <v>140</v>
       </c>
-      <c r="G9" s="179" t="s">
+      <c r="L9" s="173" t="s">
         <v>141</v>
       </c>
-      <c r="H9" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I9" s="177" t="s">
+      <c r="M9" s="173" t="s">
         <v>142</v>
       </c>
-      <c r="J9" s="175" t="s">
+      <c r="N9" s="171" t="s">
         <v>143</v>
       </c>
-      <c r="K9" s="175" t="s">
+      <c r="O9" s="171" t="s">
         <v>144</v>
       </c>
-      <c r="L9" s="173" t="s">
-        <v>145</v>
-      </c>
-      <c r="M9" s="173" t="s">
-        <v>146</v>
-      </c>
-      <c r="N9" s="171" t="s">
-        <v>147</v>
-      </c>
-      <c r="O9" s="171" t="s">
-        <v>148</v>
-      </c>
-      <c r="P9" s="203"/>
+      <c r="P9" s="191"/>
       <c r="Q9" s="183"/>
       <c r="R9" s="88"/>
       <c r="S9" s="88"/>
@@ -4856,26 +4874,26 @@
       <c r="U9" s="88"/>
     </row>
     <row r="10" spans="1:21" ht="22.5">
-      <c r="A10" s="206" t="s">
+      <c r="A10" s="194" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="195" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="196" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="196" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="180" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="207" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="208" t="s">
+      <c r="F10" s="174" t="s">
         <v>150</v>
       </c>
-      <c r="D10" s="208" t="s">
+      <c r="G10" s="178" t="s">
         <v>151</v>
-      </c>
-      <c r="E10" s="180" t="s">
-        <v>153</v>
-      </c>
-      <c r="F10" s="174" t="s">
-        <v>154</v>
-      </c>
-      <c r="G10" s="178" t="s">
-        <v>155</v>
       </c>
       <c r="H10" s="174" t="s">
         <v>83</v>
@@ -4884,25 +4902,25 @@
         <v>98</v>
       </c>
       <c r="J10" s="174" t="s">
+        <v>152</v>
+      </c>
+      <c r="K10" s="174" t="s">
+        <v>153</v>
+      </c>
+      <c r="L10" s="172" t="s">
+        <v>154</v>
+      </c>
+      <c r="M10" s="172" t="s">
+        <v>155</v>
+      </c>
+      <c r="N10" s="170" t="s">
+        <v>120</v>
+      </c>
+      <c r="O10" s="170" t="s">
         <v>156</v>
       </c>
-      <c r="K10" s="174" t="s">
-        <v>157</v>
-      </c>
-      <c r="L10" s="172" t="s">
-        <v>158</v>
-      </c>
-      <c r="M10" s="172" t="s">
-        <v>159</v>
-      </c>
-      <c r="N10" s="170" t="s">
-        <v>124</v>
-      </c>
-      <c r="O10" s="170" t="s">
-        <v>160</v>
-      </c>
-      <c r="P10" s="206" t="s">
-        <v>152</v>
+      <c r="P10" s="194" t="s">
+        <v>148</v>
       </c>
       <c r="Q10" s="183"/>
       <c r="R10" s="88"/>
@@ -4911,44 +4929,44 @@
       <c r="U10" s="88"/>
     </row>
     <row r="11" spans="1:21" ht="22.5">
-      <c r="A11" s="206"/>
-      <c r="B11" s="207"/>
-      <c r="C11" s="208"/>
-      <c r="D11" s="208"/>
+      <c r="A11" s="194"/>
+      <c r="B11" s="195"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="196"/>
       <c r="E11" s="180" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F11" s="174" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G11" s="178" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H11" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I11" s="176" t="s">
+        <v>160</v>
+      </c>
+      <c r="J11" s="174" t="s">
+        <v>161</v>
+      </c>
+      <c r="K11" s="174" t="s">
+        <v>162</v>
+      </c>
+      <c r="L11" s="172" t="s">
+        <v>163</v>
+      </c>
+      <c r="M11" s="172" t="s">
         <v>164</v>
       </c>
-      <c r="J11" s="174" t="s">
+      <c r="N11" s="170" t="s">
         <v>165</v>
       </c>
-      <c r="K11" s="174" t="s">
-        <v>166</v>
-      </c>
-      <c r="L11" s="172" t="s">
-        <v>167</v>
-      </c>
-      <c r="M11" s="172" t="s">
-        <v>168</v>
-      </c>
-      <c r="N11" s="170" t="s">
-        <v>169</v>
-      </c>
       <c r="O11" s="170" t="s">
-        <v>125</v>
-      </c>
-      <c r="P11" s="206"/>
+        <v>121</v>
+      </c>
+      <c r="P11" s="194"/>
       <c r="Q11" s="183"/>
       <c r="R11" s="88"/>
       <c r="S11" s="88"/>
@@ -4956,53 +4974,53 @@
       <c r="U11" s="88"/>
     </row>
     <row r="12" spans="1:21" ht="22.5">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="204" t="s">
+      <c r="B12" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="205" t="s">
+      <c r="C12" s="193" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="193" t="s">
+        <v>167</v>
+      </c>
+      <c r="E12" s="181" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12" s="175" t="s">
         <v>170</v>
       </c>
-      <c r="D12" s="205" t="s">
+      <c r="G12" s="179" t="s">
         <v>171</v>
-      </c>
-      <c r="E12" s="181" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" s="175" t="s">
-        <v>174</v>
-      </c>
-      <c r="G12" s="179" t="s">
-        <v>175</v>
       </c>
       <c r="H12" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I12" s="177" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="175" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="175" t="s">
+        <v>174</v>
+      </c>
+      <c r="L12" s="173" t="s">
+        <v>175</v>
+      </c>
+      <c r="M12" s="173" t="s">
         <v>176</v>
       </c>
-      <c r="J12" s="175" t="s">
+      <c r="N12" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="K12" s="175" t="s">
+      <c r="O12" s="171" t="s">
         <v>178</v>
       </c>
-      <c r="L12" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="M12" s="173" t="s">
-        <v>180</v>
-      </c>
-      <c r="N12" s="171" t="s">
-        <v>181</v>
-      </c>
-      <c r="O12" s="171" t="s">
-        <v>182</v>
-      </c>
-      <c r="P12" s="203" t="s">
-        <v>172</v>
+      <c r="P12" s="191" t="s">
+        <v>168</v>
       </c>
       <c r="Q12" s="183"/>
       <c r="R12" s="88"/>
@@ -5011,44 +5029,44 @@
       <c r="U12" s="88"/>
     </row>
     <row r="13" spans="1:21" ht="22.5">
-      <c r="A13" s="203"/>
-      <c r="B13" s="204"/>
-      <c r="C13" s="205"/>
-      <c r="D13" s="205"/>
+      <c r="A13" s="191"/>
+      <c r="B13" s="192"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
       <c r="E13" s="181" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="175" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="179" t="s">
+        <v>181</v>
+      </c>
+      <c r="H13" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" s="177" t="s">
+        <v>182</v>
+      </c>
+      <c r="J13" s="175" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="175" t="s">
+      <c r="K13" s="175" t="s">
         <v>184</v>
       </c>
-      <c r="G13" s="179" t="s">
+      <c r="L13" s="173" t="s">
         <v>185</v>
       </c>
-      <c r="H13" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I13" s="177" t="s">
+      <c r="M13" s="173" t="s">
         <v>186</v>
       </c>
-      <c r="J13" s="175" t="s">
+      <c r="N13" s="171" t="s">
         <v>187</v>
       </c>
-      <c r="K13" s="175" t="s">
+      <c r="O13" s="171" t="s">
         <v>188</v>
       </c>
-      <c r="L13" s="173" t="s">
-        <v>189</v>
-      </c>
-      <c r="M13" s="173" t="s">
-        <v>190</v>
-      </c>
-      <c r="N13" s="171" t="s">
-        <v>191</v>
-      </c>
-      <c r="O13" s="171" t="s">
-        <v>192</v>
-      </c>
-      <c r="P13" s="203"/>
+      <c r="P13" s="191"/>
       <c r="Q13" s="183"/>
       <c r="R13" s="88"/>
       <c r="S13" s="88"/>
@@ -5056,53 +5074,53 @@
       <c r="U13" s="88"/>
     </row>
     <row r="14" spans="1:21" ht="22.5">
-      <c r="A14" s="206" t="s">
+      <c r="A14" s="194" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="207" t="s">
+      <c r="B14" s="195" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="208" t="s">
+      <c r="C14" s="196" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="196" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="180" t="s">
+        <v>192</v>
+      </c>
+      <c r="F14" s="174" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="208" t="s">
+      <c r="G14" s="178" t="s">
         <v>194</v>
-      </c>
-      <c r="E14" s="180" t="s">
-        <v>196</v>
-      </c>
-      <c r="F14" s="174" t="s">
-        <v>197</v>
-      </c>
-      <c r="G14" s="178" t="s">
-        <v>198</v>
       </c>
       <c r="H14" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I14" s="176" t="s">
+        <v>195</v>
+      </c>
+      <c r="J14" s="174" t="s">
+        <v>196</v>
+      </c>
+      <c r="K14" s="174" t="s">
+        <v>197</v>
+      </c>
+      <c r="L14" s="172" t="s">
+        <v>198</v>
+      </c>
+      <c r="M14" s="172" t="s">
         <v>199</v>
       </c>
-      <c r="J14" s="174" t="s">
+      <c r="N14" s="170" t="s">
         <v>200</v>
       </c>
-      <c r="K14" s="174" t="s">
+      <c r="O14" s="170" t="s">
         <v>201</v>
       </c>
-      <c r="L14" s="172" t="s">
-        <v>202</v>
-      </c>
-      <c r="M14" s="172" t="s">
-        <v>203</v>
-      </c>
-      <c r="N14" s="170" t="s">
-        <v>204</v>
-      </c>
-      <c r="O14" s="170" t="s">
-        <v>205</v>
-      </c>
-      <c r="P14" s="206" t="s">
-        <v>195</v>
+      <c r="P14" s="194" t="s">
+        <v>191</v>
       </c>
       <c r="Q14" s="183"/>
       <c r="R14" s="88"/>
@@ -5111,44 +5129,44 @@
       <c r="U14" s="88"/>
     </row>
     <row r="15" spans="1:21" ht="22.5">
-      <c r="A15" s="206"/>
-      <c r="B15" s="207"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="208"/>
+      <c r="A15" s="194"/>
+      <c r="B15" s="195"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="196"/>
       <c r="E15" s="180" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="174" t="s">
+        <v>203</v>
+      </c>
+      <c r="G15" s="178" t="s">
+        <v>204</v>
+      </c>
+      <c r="H15" s="174" t="s">
+        <v>129</v>
+      </c>
+      <c r="I15" s="176" t="s">
+        <v>205</v>
+      </c>
+      <c r="J15" s="174" t="s">
         <v>206</v>
       </c>
-      <c r="F15" s="174" t="s">
+      <c r="K15" s="174" t="s">
         <v>207</v>
       </c>
-      <c r="G15" s="178" t="s">
+      <c r="L15" s="172" t="s">
         <v>208</v>
       </c>
-      <c r="H15" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="I15" s="176" t="s">
+      <c r="M15" s="172" t="s">
         <v>209</v>
       </c>
-      <c r="J15" s="174" t="s">
+      <c r="N15" s="170" t="s">
         <v>210</v>
       </c>
-      <c r="K15" s="174" t="s">
+      <c r="O15" s="170" t="s">
         <v>211</v>
       </c>
-      <c r="L15" s="172" t="s">
-        <v>212</v>
-      </c>
-      <c r="M15" s="172" t="s">
-        <v>213</v>
-      </c>
-      <c r="N15" s="170" t="s">
-        <v>214</v>
-      </c>
-      <c r="O15" s="170" t="s">
-        <v>215</v>
-      </c>
-      <c r="P15" s="206"/>
+      <c r="P15" s="194"/>
       <c r="Q15" s="183"/>
       <c r="R15" s="88"/>
       <c r="S15" s="88"/>
@@ -5163,46 +5181,46 @@
         <v>76</v>
       </c>
       <c r="C16" s="187" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="187" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>215</v>
+      </c>
+      <c r="F16" s="175" t="s">
         <v>216</v>
       </c>
-      <c r="D16" s="187" t="s">
+      <c r="G16" s="179" t="s">
         <v>217</v>
       </c>
-      <c r="E16" s="181" t="s">
+      <c r="H16" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I16" s="177" t="s">
+        <v>218</v>
+      </c>
+      <c r="J16" s="175" t="s">
         <v>219</v>
       </c>
-      <c r="F16" s="175" t="s">
+      <c r="K16" s="175" t="s">
         <v>220</v>
       </c>
-      <c r="G16" s="179" t="s">
+      <c r="L16" s="173" t="s">
         <v>221</v>
       </c>
-      <c r="H16" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I16" s="177" t="s">
+      <c r="M16" s="173" t="s">
         <v>222</v>
       </c>
-      <c r="J16" s="175" t="s">
+      <c r="N16" s="171" t="s">
         <v>223</v>
       </c>
-      <c r="K16" s="175" t="s">
+      <c r="O16" s="171" t="s">
         <v>224</v>
       </c>
-      <c r="L16" s="173" t="s">
-        <v>225</v>
-      </c>
-      <c r="M16" s="173" t="s">
-        <v>226</v>
-      </c>
-      <c r="N16" s="171" t="s">
-        <v>227</v>
-      </c>
-      <c r="O16" s="171" t="s">
-        <v>228</v>
-      </c>
       <c r="P16" s="169" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q16" s="183"/>
       <c r="R16" s="88"/>
@@ -5211,53 +5229,53 @@
       <c r="U16" s="88"/>
     </row>
     <row r="17" spans="1:21" ht="22.5">
-      <c r="A17" s="206" t="s">
+      <c r="A17" s="194" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="207" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" s="208" t="s">
+      <c r="B17" s="195" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="196" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="196" t="s">
+        <v>226</v>
+      </c>
+      <c r="E17" s="180" t="s">
+        <v>228</v>
+      </c>
+      <c r="F17" s="174" t="s">
         <v>229</v>
       </c>
-      <c r="D17" s="208" t="s">
+      <c r="G17" s="178" t="s">
         <v>230</v>
-      </c>
-      <c r="E17" s="180" t="s">
-        <v>232</v>
-      </c>
-      <c r="F17" s="174" t="s">
-        <v>233</v>
-      </c>
-      <c r="G17" s="178" t="s">
-        <v>234</v>
       </c>
       <c r="H17" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I17" s="176" t="s">
+        <v>231</v>
+      </c>
+      <c r="J17" s="174" t="s">
+        <v>232</v>
+      </c>
+      <c r="K17" s="174" t="s">
+        <v>233</v>
+      </c>
+      <c r="L17" s="172" t="s">
+        <v>234</v>
+      </c>
+      <c r="M17" s="172" t="s">
         <v>235</v>
       </c>
-      <c r="J17" s="174" t="s">
+      <c r="N17" s="170" t="s">
         <v>236</v>
       </c>
-      <c r="K17" s="174" t="s">
+      <c r="O17" s="170" t="s">
         <v>237</v>
       </c>
-      <c r="L17" s="172" t="s">
-        <v>238</v>
-      </c>
-      <c r="M17" s="172" t="s">
-        <v>239</v>
-      </c>
-      <c r="N17" s="170" t="s">
-        <v>240</v>
-      </c>
-      <c r="O17" s="170" t="s">
-        <v>241</v>
-      </c>
-      <c r="P17" s="206" t="s">
-        <v>231</v>
+      <c r="P17" s="194" t="s">
+        <v>227</v>
       </c>
       <c r="Q17" s="183"/>
       <c r="R17" s="88"/>
@@ -5266,44 +5284,44 @@
       <c r="U17" s="88"/>
     </row>
     <row r="18" spans="1:21" ht="45">
-      <c r="A18" s="206"/>
-      <c r="B18" s="207"/>
-      <c r="C18" s="208"/>
-      <c r="D18" s="208"/>
+      <c r="A18" s="194"/>
+      <c r="B18" s="195"/>
+      <c r="C18" s="196"/>
+      <c r="D18" s="196"/>
       <c r="E18" s="180" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F18" s="174" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G18" s="178" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H18" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I18" s="176" t="s">
+        <v>241</v>
+      </c>
+      <c r="J18" s="174" t="s">
+        <v>242</v>
+      </c>
+      <c r="K18" s="174" t="s">
+        <v>243</v>
+      </c>
+      <c r="L18" s="172" t="s">
+        <v>244</v>
+      </c>
+      <c r="M18" s="172" t="s">
         <v>245</v>
       </c>
-      <c r="J18" s="174" t="s">
+      <c r="N18" s="170" t="s">
         <v>246</v>
       </c>
-      <c r="K18" s="174" t="s">
+      <c r="O18" s="170" t="s">
         <v>247</v>
       </c>
-      <c r="L18" s="172" t="s">
-        <v>248</v>
-      </c>
-      <c r="M18" s="172" t="s">
-        <v>249</v>
-      </c>
-      <c r="N18" s="170" t="s">
-        <v>250</v>
-      </c>
-      <c r="O18" s="170" t="s">
-        <v>251</v>
-      </c>
-      <c r="P18" s="206"/>
+      <c r="P18" s="194"/>
       <c r="Q18" s="183"/>
       <c r="R18" s="88"/>
       <c r="S18" s="88"/>
@@ -5318,46 +5336,46 @@
         <v>76</v>
       </c>
       <c r="C19" s="187" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="187" t="s">
+        <v>249</v>
+      </c>
+      <c r="E19" s="181" t="s">
+        <v>251</v>
+      </c>
+      <c r="F19" s="175" t="s">
         <v>252</v>
       </c>
-      <c r="D19" s="187" t="s">
+      <c r="G19" s="179" t="s">
         <v>253</v>
       </c>
-      <c r="E19" s="181" t="s">
+      <c r="H19" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I19" s="177" t="s">
+        <v>254</v>
+      </c>
+      <c r="J19" s="175" t="s">
         <v>255</v>
       </c>
-      <c r="F19" s="175" t="s">
+      <c r="K19" s="175" t="s">
         <v>256</v>
       </c>
-      <c r="G19" s="179" t="s">
+      <c r="L19" s="173" t="s">
         <v>257</v>
       </c>
-      <c r="H19" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I19" s="177" t="s">
+      <c r="M19" s="173" t="s">
         <v>258</v>
       </c>
-      <c r="J19" s="175" t="s">
+      <c r="N19" s="171" t="s">
         <v>259</v>
       </c>
-      <c r="K19" s="175" t="s">
+      <c r="O19" s="171" t="s">
         <v>260</v>
       </c>
-      <c r="L19" s="173" t="s">
-        <v>261</v>
-      </c>
-      <c r="M19" s="173" t="s">
-        <v>262</v>
-      </c>
-      <c r="N19" s="171" t="s">
-        <v>263</v>
-      </c>
-      <c r="O19" s="171" t="s">
-        <v>264</v>
-      </c>
       <c r="P19" s="169" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="Q19" s="183"/>
       <c r="R19" s="88"/>
@@ -5366,53 +5384,53 @@
       <c r="U19" s="88"/>
     </row>
     <row r="20" spans="1:21" ht="22.5">
-      <c r="A20" s="206" t="s">
+      <c r="A20" s="194" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="207" t="s">
+      <c r="B20" s="195" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="208" t="s">
+      <c r="C20" s="196" t="s">
+        <v>261</v>
+      </c>
+      <c r="D20" s="196" t="s">
+        <v>262</v>
+      </c>
+      <c r="E20" s="167" t="s">
+        <v>264</v>
+      </c>
+      <c r="F20" s="174" t="s">
         <v>265</v>
       </c>
-      <c r="D20" s="208" t="s">
+      <c r="G20" s="178" t="s">
         <v>266</v>
-      </c>
-      <c r="E20" s="167" t="s">
-        <v>268</v>
-      </c>
-      <c r="F20" s="174" t="s">
-        <v>269</v>
-      </c>
-      <c r="G20" s="178" t="s">
-        <v>270</v>
       </c>
       <c r="H20" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I20" s="176" t="s">
+        <v>267</v>
+      </c>
+      <c r="J20" s="174" t="s">
+        <v>268</v>
+      </c>
+      <c r="K20" s="174" t="s">
+        <v>269</v>
+      </c>
+      <c r="L20" s="172" t="s">
+        <v>270</v>
+      </c>
+      <c r="M20" s="172" t="s">
         <v>271</v>
       </c>
-      <c r="J20" s="174" t="s">
+      <c r="N20" s="170" t="s">
+        <v>256</v>
+      </c>
+      <c r="O20" s="170" t="s">
         <v>272</v>
       </c>
-      <c r="K20" s="174" t="s">
-        <v>273</v>
-      </c>
-      <c r="L20" s="172" t="s">
-        <v>274</v>
-      </c>
-      <c r="M20" s="172" t="s">
-        <v>275</v>
-      </c>
-      <c r="N20" s="170" t="s">
-        <v>260</v>
-      </c>
-      <c r="O20" s="170" t="s">
-        <v>276</v>
-      </c>
-      <c r="P20" s="206" t="s">
-        <v>267</v>
+      <c r="P20" s="194" t="s">
+        <v>263</v>
       </c>
       <c r="Q20" s="183"/>
       <c r="R20" s="88"/>
@@ -5421,44 +5439,44 @@
       <c r="U20" s="88"/>
     </row>
     <row r="21" spans="1:21" ht="22.5">
-      <c r="A21" s="206"/>
-      <c r="B21" s="207"/>
-      <c r="C21" s="208"/>
-      <c r="D21" s="208"/>
+      <c r="A21" s="194"/>
+      <c r="B21" s="195"/>
+      <c r="C21" s="196"/>
+      <c r="D21" s="196"/>
       <c r="E21" s="167" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F21" s="174" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G21" s="178" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H21" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I21" s="176" t="s">
+        <v>275</v>
+      </c>
+      <c r="J21" s="174" t="s">
+        <v>276</v>
+      </c>
+      <c r="K21" s="174" t="s">
+        <v>277</v>
+      </c>
+      <c r="L21" s="172" t="s">
+        <v>278</v>
+      </c>
+      <c r="M21" s="172" t="s">
         <v>279</v>
-      </c>
-      <c r="J21" s="174" t="s">
-        <v>280</v>
-      </c>
-      <c r="K21" s="174" t="s">
-        <v>281</v>
-      </c>
-      <c r="L21" s="172" t="s">
-        <v>282</v>
-      </c>
-      <c r="M21" s="172" t="s">
-        <v>283</v>
       </c>
       <c r="N21" s="170" t="s">
         <v>99</v>
       </c>
       <c r="O21" s="170" t="s">
-        <v>284</v>
-      </c>
-      <c r="P21" s="206"/>
+        <v>280</v>
+      </c>
+      <c r="P21" s="194"/>
       <c r="Q21" s="183"/>
       <c r="R21" s="88"/>
       <c r="S21" s="88"/>
@@ -5473,46 +5491,46 @@
         <v>76</v>
       </c>
       <c r="C22" s="187" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" s="187" t="s">
+        <v>282</v>
+      </c>
+      <c r="E22" s="181" t="s">
+        <v>284</v>
+      </c>
+      <c r="F22" s="175" t="s">
         <v>285</v>
       </c>
-      <c r="D22" s="187" t="s">
+      <c r="G22" s="179" t="s">
         <v>286</v>
       </c>
-      <c r="E22" s="181" t="s">
+      <c r="H22" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" s="177" t="s">
+        <v>287</v>
+      </c>
+      <c r="J22" s="175" t="s">
         <v>288</v>
       </c>
-      <c r="F22" s="175" t="s">
+      <c r="K22" s="175" t="s">
         <v>289</v>
       </c>
-      <c r="G22" s="179" t="s">
+      <c r="L22" s="173" t="s">
         <v>290</v>
       </c>
-      <c r="H22" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I22" s="177" t="s">
+      <c r="M22" s="173" t="s">
         <v>291</v>
       </c>
-      <c r="J22" s="175" t="s">
+      <c r="N22" s="171" t="s">
         <v>292</v>
       </c>
-      <c r="K22" s="175" t="s">
+      <c r="O22" s="171" t="s">
         <v>293</v>
       </c>
-      <c r="L22" s="173" t="s">
-        <v>294</v>
-      </c>
-      <c r="M22" s="173" t="s">
-        <v>295</v>
-      </c>
-      <c r="N22" s="171" t="s">
-        <v>296</v>
-      </c>
-      <c r="O22" s="171" t="s">
-        <v>297</v>
-      </c>
       <c r="P22" s="169" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="Q22" s="183"/>
       <c r="R22" s="88"/>
@@ -5528,46 +5546,46 @@
         <v>76</v>
       </c>
       <c r="C23" s="186" t="s">
+        <v>294</v>
+      </c>
+      <c r="D23" s="186" t="s">
+        <v>295</v>
+      </c>
+      <c r="E23" s="167" t="s">
+        <v>296</v>
+      </c>
+      <c r="F23" s="174" t="s">
+        <v>297</v>
+      </c>
+      <c r="G23" s="178" t="s">
         <v>298</v>
       </c>
-      <c r="D23" s="186" t="s">
+      <c r="H23" s="174" t="s">
+        <v>129</v>
+      </c>
+      <c r="I23" s="176" t="s">
         <v>299</v>
       </c>
-      <c r="E23" s="167" t="s">
+      <c r="J23" s="174" t="s">
         <v>300</v>
       </c>
-      <c r="F23" s="174" t="s">
+      <c r="K23" s="174" t="s">
         <v>301</v>
       </c>
-      <c r="G23" s="178" t="s">
+      <c r="L23" s="172" t="s">
+        <v>198</v>
+      </c>
+      <c r="M23" s="172" t="s">
         <v>302</v>
       </c>
-      <c r="H23" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="I23" s="176" t="s">
+      <c r="N23" s="170" t="s">
         <v>303</v>
       </c>
-      <c r="J23" s="174" t="s">
+      <c r="O23" s="170" t="s">
         <v>304</v>
       </c>
-      <c r="K23" s="174" t="s">
-        <v>305</v>
-      </c>
-      <c r="L23" s="172" t="s">
-        <v>202</v>
-      </c>
-      <c r="M23" s="172" t="s">
-        <v>306</v>
-      </c>
-      <c r="N23" s="170" t="s">
-        <v>307</v>
-      </c>
-      <c r="O23" s="170" t="s">
-        <v>308</v>
-      </c>
       <c r="P23" s="168" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="Q23" s="183"/>
       <c r="R23" s="88"/>
@@ -5576,53 +5594,53 @@
       <c r="U23" s="88"/>
     </row>
     <row r="24" spans="1:21" ht="56.25">
-      <c r="A24" s="203" t="s">
+      <c r="A24" s="191" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="204" t="s">
+      <c r="B24" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="205" t="s">
+      <c r="C24" s="193" t="s">
+        <v>305</v>
+      </c>
+      <c r="D24" s="193" t="s">
+        <v>306</v>
+      </c>
+      <c r="E24" s="182" t="s">
+        <v>307</v>
+      </c>
+      <c r="F24" s="175" t="s">
+        <v>308</v>
+      </c>
+      <c r="G24" s="179" t="s">
         <v>309</v>
-      </c>
-      <c r="D24" s="205" t="s">
-        <v>310</v>
-      </c>
-      <c r="E24" s="182" t="s">
-        <v>311</v>
-      </c>
-      <c r="F24" s="175" t="s">
-        <v>312</v>
-      </c>
-      <c r="G24" s="179" t="s">
-        <v>313</v>
       </c>
       <c r="H24" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I24" s="177" t="s">
+        <v>310</v>
+      </c>
+      <c r="J24" s="175" t="s">
+        <v>311</v>
+      </c>
+      <c r="K24" s="175" t="s">
+        <v>312</v>
+      </c>
+      <c r="L24" s="173" t="s">
+        <v>313</v>
+      </c>
+      <c r="M24" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="J24" s="175" t="s">
-        <v>315</v>
-      </c>
-      <c r="K24" s="175" t="s">
-        <v>316</v>
-      </c>
-      <c r="L24" s="173" t="s">
-        <v>317</v>
-      </c>
-      <c r="M24" s="173" t="s">
-        <v>318</v>
-      </c>
       <c r="N24" s="171" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="O24" s="171" t="s">
-        <v>215</v>
-      </c>
-      <c r="P24" s="203" t="s">
-        <v>287</v>
+        <v>211</v>
+      </c>
+      <c r="P24" s="191" t="s">
+        <v>283</v>
       </c>
       <c r="Q24" s="183"/>
       <c r="R24" s="88"/>
@@ -5631,44 +5649,44 @@
       <c r="U24" s="88"/>
     </row>
     <row r="25" spans="1:21" ht="67.5">
-      <c r="A25" s="203"/>
-      <c r="B25" s="204"/>
-      <c r="C25" s="205"/>
-      <c r="D25" s="205"/>
+      <c r="A25" s="191"/>
+      <c r="B25" s="192"/>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
       <c r="E25" s="181" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F25" s="175" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G25" s="179" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="H25" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I25" s="177" t="s">
+        <v>317</v>
+      </c>
+      <c r="J25" s="175" t="s">
+        <v>318</v>
+      </c>
+      <c r="K25" s="175" t="s">
+        <v>256</v>
+      </c>
+      <c r="L25" s="173" t="s">
+        <v>319</v>
+      </c>
+      <c r="M25" s="173" t="s">
+        <v>320</v>
+      </c>
+      <c r="N25" s="171" t="s">
         <v>321</v>
       </c>
-      <c r="J25" s="175" t="s">
+      <c r="O25" s="171" t="s">
         <v>322</v>
       </c>
-      <c r="K25" s="175" t="s">
-        <v>260</v>
-      </c>
-      <c r="L25" s="173" t="s">
-        <v>323</v>
-      </c>
-      <c r="M25" s="173" t="s">
-        <v>324</v>
-      </c>
-      <c r="N25" s="171" t="s">
-        <v>325</v>
-      </c>
-      <c r="O25" s="171" t="s">
-        <v>326</v>
-      </c>
-      <c r="P25" s="203"/>
+      <c r="P25" s="191"/>
       <c r="Q25" s="183"/>
       <c r="R25" s="88"/>
       <c r="S25" s="88"/>
@@ -5676,53 +5694,53 @@
       <c r="U25" s="88"/>
     </row>
     <row r="26" spans="1:21" ht="22.5">
-      <c r="A26" s="206" t="s">
+      <c r="A26" s="194" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="207" t="s">
+      <c r="B26" s="195" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="208" t="s">
+      <c r="C26" s="196" t="s">
+        <v>323</v>
+      </c>
+      <c r="D26" s="196" t="s">
+        <v>324</v>
+      </c>
+      <c r="E26" s="180" t="s">
+        <v>326</v>
+      </c>
+      <c r="F26" s="174" t="s">
         <v>327</v>
       </c>
-      <c r="D26" s="208" t="s">
+      <c r="G26" s="178" t="s">
         <v>328</v>
-      </c>
-      <c r="E26" s="180" t="s">
-        <v>330</v>
-      </c>
-      <c r="F26" s="174" t="s">
-        <v>331</v>
-      </c>
-      <c r="G26" s="178" t="s">
-        <v>332</v>
       </c>
       <c r="H26" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I26" s="176" t="s">
+        <v>329</v>
+      </c>
+      <c r="J26" s="174" t="s">
+        <v>330</v>
+      </c>
+      <c r="K26" s="174" t="s">
+        <v>331</v>
+      </c>
+      <c r="L26" s="172" t="s">
+        <v>332</v>
+      </c>
+      <c r="M26" s="172" t="s">
         <v>333</v>
       </c>
-      <c r="J26" s="174" t="s">
+      <c r="N26" s="170" t="s">
         <v>334</v>
       </c>
-      <c r="K26" s="174" t="s">
+      <c r="O26" s="170" t="s">
         <v>335</v>
       </c>
-      <c r="L26" s="172" t="s">
-        <v>336</v>
-      </c>
-      <c r="M26" s="172" t="s">
-        <v>337</v>
-      </c>
-      <c r="N26" s="170" t="s">
-        <v>338</v>
-      </c>
-      <c r="O26" s="170" t="s">
-        <v>339</v>
-      </c>
-      <c r="P26" s="206" t="s">
-        <v>329</v>
+      <c r="P26" s="194" t="s">
+        <v>325</v>
       </c>
       <c r="Q26" s="183"/>
       <c r="R26" s="88"/>
@@ -5731,44 +5749,44 @@
       <c r="U26" s="88"/>
     </row>
     <row r="27" spans="1:21" ht="22.5">
-      <c r="A27" s="206"/>
-      <c r="B27" s="207"/>
-      <c r="C27" s="208"/>
-      <c r="D27" s="208"/>
+      <c r="A27" s="194"/>
+      <c r="B27" s="195"/>
+      <c r="C27" s="196"/>
+      <c r="D27" s="196"/>
       <c r="E27" s="180" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F27" s="174" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G27" s="178" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H27" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I27" s="176" t="s">
+        <v>339</v>
+      </c>
+      <c r="J27" s="174" t="s">
+        <v>340</v>
+      </c>
+      <c r="K27" s="174" t="s">
+        <v>341</v>
+      </c>
+      <c r="L27" s="172" t="s">
+        <v>342</v>
+      </c>
+      <c r="M27" s="172" t="s">
+        <v>221</v>
+      </c>
+      <c r="N27" s="170" t="s">
         <v>343</v>
       </c>
-      <c r="J27" s="174" t="s">
-        <v>344</v>
-      </c>
-      <c r="K27" s="174" t="s">
-        <v>345</v>
-      </c>
-      <c r="L27" s="172" t="s">
-        <v>346</v>
-      </c>
-      <c r="M27" s="172" t="s">
-        <v>225</v>
-      </c>
-      <c r="N27" s="170" t="s">
-        <v>347</v>
-      </c>
       <c r="O27" s="170" t="s">
-        <v>148</v>
-      </c>
-      <c r="P27" s="206"/>
+        <v>144</v>
+      </c>
+      <c r="P27" s="194"/>
       <c r="Q27" s="183"/>
       <c r="R27" s="88"/>
       <c r="S27" s="88"/>
@@ -5776,53 +5794,53 @@
       <c r="U27" s="88"/>
     </row>
     <row r="28" spans="1:21" ht="33.75">
-      <c r="A28" s="203" t="s">
+      <c r="A28" s="191" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="204" t="s">
+      <c r="B28" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="205" t="s">
+      <c r="C28" s="193" t="s">
+        <v>344</v>
+      </c>
+      <c r="D28" s="193" t="s">
+        <v>345</v>
+      </c>
+      <c r="E28" s="181" t="s">
+        <v>347</v>
+      </c>
+      <c r="F28" s="175" t="s">
         <v>348</v>
       </c>
-      <c r="D28" s="205" t="s">
+      <c r="G28" s="179" t="s">
         <v>349</v>
-      </c>
-      <c r="E28" s="181" t="s">
-        <v>351</v>
-      </c>
-      <c r="F28" s="175" t="s">
-        <v>352</v>
-      </c>
-      <c r="G28" s="179" t="s">
-        <v>353</v>
       </c>
       <c r="H28" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I28" s="177" t="s">
+        <v>350</v>
+      </c>
+      <c r="J28" s="175" t="s">
+        <v>351</v>
+      </c>
+      <c r="K28" s="175" t="s">
+        <v>352</v>
+      </c>
+      <c r="L28" s="173" t="s">
+        <v>353</v>
+      </c>
+      <c r="M28" s="173" t="s">
         <v>354</v>
       </c>
-      <c r="J28" s="175" t="s">
+      <c r="N28" s="171" t="s">
         <v>355</v>
       </c>
-      <c r="K28" s="175" t="s">
+      <c r="O28" s="171" t="s">
         <v>356</v>
       </c>
-      <c r="L28" s="173" t="s">
-        <v>357</v>
-      </c>
-      <c r="M28" s="173" t="s">
-        <v>358</v>
-      </c>
-      <c r="N28" s="171" t="s">
-        <v>359</v>
-      </c>
-      <c r="O28" s="171" t="s">
-        <v>360</v>
-      </c>
-      <c r="P28" s="203" t="s">
-        <v>350</v>
+      <c r="P28" s="191" t="s">
+        <v>346</v>
       </c>
       <c r="Q28" s="183"/>
       <c r="R28" s="88"/>
@@ -5831,44 +5849,44 @@
       <c r="U28" s="88"/>
     </row>
     <row r="29" spans="1:21" ht="22.5">
-      <c r="A29" s="203"/>
-      <c r="B29" s="204"/>
-      <c r="C29" s="205"/>
-      <c r="D29" s="205"/>
+      <c r="A29" s="191"/>
+      <c r="B29" s="192"/>
+      <c r="C29" s="193"/>
+      <c r="D29" s="193"/>
       <c r="E29" s="181" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F29" s="175" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G29" s="179" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H29" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I29" s="177" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J29" s="175" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K29" s="175" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="L29" s="173" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M29" s="173" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="N29" s="171" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O29" s="171" t="s">
-        <v>322</v>
-      </c>
-      <c r="P29" s="203"/>
+        <v>318</v>
+      </c>
+      <c r="P29" s="191"/>
       <c r="Q29" s="183"/>
       <c r="R29" s="88"/>
       <c r="S29" s="88"/>
@@ -5876,44 +5894,44 @@
       <c r="U29" s="88"/>
     </row>
     <row r="30" spans="1:21" ht="33.75">
-      <c r="A30" s="203"/>
-      <c r="B30" s="204"/>
-      <c r="C30" s="205"/>
-      <c r="D30" s="205"/>
+      <c r="A30" s="191"/>
+      <c r="B30" s="192"/>
+      <c r="C30" s="193"/>
+      <c r="D30" s="193"/>
       <c r="E30" s="181" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F30" s="175" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G30" s="179" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H30" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I30" s="177" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J30" s="175" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K30" s="175" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="L30" s="173" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="M30" s="173" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="N30" s="171" t="s">
         <v>99</v>
       </c>
       <c r="O30" s="171" t="s">
-        <v>181</v>
-      </c>
-      <c r="P30" s="203"/>
+        <v>177</v>
+      </c>
+      <c r="P30" s="191"/>
       <c r="Q30" s="183"/>
       <c r="R30" s="88"/>
       <c r="S30" s="88"/>
@@ -5921,44 +5939,44 @@
       <c r="U30" s="88"/>
     </row>
     <row r="31" spans="1:21" ht="22.5">
-      <c r="A31" s="203"/>
-      <c r="B31" s="204"/>
-      <c r="C31" s="205"/>
-      <c r="D31" s="205"/>
+      <c r="A31" s="191"/>
+      <c r="B31" s="192"/>
+      <c r="C31" s="193"/>
+      <c r="D31" s="193"/>
       <c r="E31" s="181" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F31" s="175" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G31" s="179" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="H31" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I31" s="177" t="s">
+        <v>370</v>
+      </c>
+      <c r="J31" s="175" t="s">
+        <v>371</v>
+      </c>
+      <c r="K31" s="175" t="s">
+        <v>372</v>
+      </c>
+      <c r="L31" s="173" t="s">
+        <v>373</v>
+      </c>
+      <c r="M31" s="173" t="s">
         <v>374</v>
       </c>
-      <c r="J31" s="175" t="s">
+      <c r="N31" s="171" t="s">
+        <v>259</v>
+      </c>
+      <c r="O31" s="171" t="s">
         <v>375</v>
       </c>
-      <c r="K31" s="175" t="s">
-        <v>376</v>
-      </c>
-      <c r="L31" s="173" t="s">
-        <v>377</v>
-      </c>
-      <c r="M31" s="173" t="s">
-        <v>378</v>
-      </c>
-      <c r="N31" s="171" t="s">
-        <v>263</v>
-      </c>
-      <c r="O31" s="171" t="s">
-        <v>379</v>
-      </c>
-      <c r="P31" s="203"/>
+      <c r="P31" s="191"/>
       <c r="Q31" s="183"/>
       <c r="R31" s="88"/>
       <c r="S31" s="88"/>
@@ -5966,53 +5984,53 @@
       <c r="U31" s="88"/>
     </row>
     <row r="32" spans="1:21" ht="22.5">
-      <c r="A32" s="206" t="s">
+      <c r="A32" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="207" t="s">
+      <c r="B32" s="195" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="208" t="s">
+      <c r="C32" s="196" t="s">
+        <v>376</v>
+      </c>
+      <c r="D32" s="196" t="s">
+        <v>377</v>
+      </c>
+      <c r="E32" s="180" t="s">
+        <v>378</v>
+      </c>
+      <c r="F32" s="174" t="s">
+        <v>379</v>
+      </c>
+      <c r="G32" s="178" t="s">
         <v>380</v>
-      </c>
-      <c r="D32" s="208" t="s">
-        <v>381</v>
-      </c>
-      <c r="E32" s="180" t="s">
-        <v>382</v>
-      </c>
-      <c r="F32" s="174" t="s">
-        <v>383</v>
-      </c>
-      <c r="G32" s="178" t="s">
-        <v>384</v>
       </c>
       <c r="H32" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I32" s="176" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J32" s="174" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K32" s="174" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="L32" s="172" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="M32" s="172" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="N32" s="170" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="O32" s="170" t="s">
-        <v>259</v>
-      </c>
-      <c r="P32" s="206" t="s">
-        <v>287</v>
+        <v>255</v>
+      </c>
+      <c r="P32" s="194" t="s">
+        <v>283</v>
       </c>
       <c r="Q32" s="183"/>
       <c r="R32" s="88"/>
@@ -6021,44 +6039,44 @@
       <c r="U32" s="88"/>
     </row>
     <row r="33" spans="1:21" ht="22.5">
-      <c r="A33" s="206"/>
-      <c r="B33" s="207"/>
-      <c r="C33" s="208"/>
-      <c r="D33" s="208"/>
+      <c r="A33" s="194"/>
+      <c r="B33" s="195"/>
+      <c r="C33" s="196"/>
+      <c r="D33" s="196"/>
       <c r="E33" s="180" t="s">
+        <v>385</v>
+      </c>
+      <c r="F33" s="174" t="s">
+        <v>386</v>
+      </c>
+      <c r="G33" s="178" t="s">
+        <v>387</v>
+      </c>
+      <c r="H33" s="174" t="s">
+        <v>129</v>
+      </c>
+      <c r="I33" s="176" t="s">
+        <v>388</v>
+      </c>
+      <c r="J33" s="174" t="s">
         <v>389</v>
       </c>
-      <c r="F33" s="174" t="s">
+      <c r="K33" s="174" t="s">
         <v>390</v>
       </c>
-      <c r="G33" s="178" t="s">
+      <c r="L33" s="172" t="s">
+        <v>342</v>
+      </c>
+      <c r="M33" s="172" t="s">
+        <v>155</v>
+      </c>
+      <c r="N33" s="170" t="s">
         <v>391</v>
       </c>
-      <c r="H33" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="I33" s="176" t="s">
+      <c r="O33" s="170" t="s">
         <v>392</v>
       </c>
-      <c r="J33" s="174" t="s">
-        <v>393</v>
-      </c>
-      <c r="K33" s="174" t="s">
-        <v>394</v>
-      </c>
-      <c r="L33" s="172" t="s">
-        <v>346</v>
-      </c>
-      <c r="M33" s="172" t="s">
-        <v>159</v>
-      </c>
-      <c r="N33" s="170" t="s">
-        <v>395</v>
-      </c>
-      <c r="O33" s="170" t="s">
-        <v>396</v>
-      </c>
-      <c r="P33" s="206"/>
+      <c r="P33" s="194"/>
       <c r="Q33" s="183"/>
       <c r="R33" s="88"/>
       <c r="S33" s="88"/>
@@ -6066,44 +6084,44 @@
       <c r="U33" s="88"/>
     </row>
     <row r="34" spans="1:21" ht="22.5">
-      <c r="A34" s="206"/>
-      <c r="B34" s="207"/>
-      <c r="C34" s="208"/>
-      <c r="D34" s="208"/>
+      <c r="A34" s="194"/>
+      <c r="B34" s="195"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="196"/>
       <c r="E34" s="180" t="s">
+        <v>393</v>
+      </c>
+      <c r="F34" s="174" t="s">
+        <v>394</v>
+      </c>
+      <c r="G34" s="178" t="s">
+        <v>395</v>
+      </c>
+      <c r="H34" s="174" t="s">
+        <v>129</v>
+      </c>
+      <c r="I34" s="176" t="s">
+        <v>199</v>
+      </c>
+      <c r="J34" s="174" t="s">
+        <v>396</v>
+      </c>
+      <c r="K34" s="174" t="s">
         <v>397</v>
       </c>
-      <c r="F34" s="174" t="s">
+      <c r="L34" s="172" t="s">
         <v>398</v>
       </c>
-      <c r="G34" s="178" t="s">
+      <c r="M34" s="172" t="s">
         <v>399</v>
       </c>
-      <c r="H34" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="I34" s="176" t="s">
-        <v>203</v>
-      </c>
-      <c r="J34" s="174" t="s">
+      <c r="N34" s="170" t="s">
         <v>400</v>
       </c>
-      <c r="K34" s="174" t="s">
+      <c r="O34" s="170" t="s">
         <v>401</v>
       </c>
-      <c r="L34" s="172" t="s">
-        <v>402</v>
-      </c>
-      <c r="M34" s="172" t="s">
-        <v>403</v>
-      </c>
-      <c r="N34" s="170" t="s">
-        <v>404</v>
-      </c>
-      <c r="O34" s="170" t="s">
-        <v>405</v>
-      </c>
-      <c r="P34" s="206"/>
+      <c r="P34" s="194"/>
       <c r="Q34" s="183"/>
       <c r="R34" s="88"/>
       <c r="S34" s="88"/>
@@ -6111,53 +6129,53 @@
       <c r="U34" s="88"/>
     </row>
     <row r="35" spans="1:21" ht="22.5">
-      <c r="A35" s="203" t="s">
+      <c r="A35" s="191" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="204" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" s="205" t="s">
+      <c r="B35" s="192" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="193" t="s">
+        <v>402</v>
+      </c>
+      <c r="D35" s="193" t="s">
+        <v>403</v>
+      </c>
+      <c r="E35" s="181" t="s">
+        <v>405</v>
+      </c>
+      <c r="F35" s="175" t="s">
         <v>406</v>
       </c>
-      <c r="D35" s="205" t="s">
+      <c r="G35" s="179" t="s">
         <v>407</v>
-      </c>
-      <c r="E35" s="181" t="s">
-        <v>409</v>
-      </c>
-      <c r="F35" s="175" t="s">
-        <v>410</v>
-      </c>
-      <c r="G35" s="179" t="s">
-        <v>411</v>
       </c>
       <c r="H35" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I35" s="177" t="s">
+        <v>408</v>
+      </c>
+      <c r="J35" s="175" t="s">
+        <v>409</v>
+      </c>
+      <c r="K35" s="175" t="s">
+        <v>410</v>
+      </c>
+      <c r="L35" s="173" t="s">
+        <v>411</v>
+      </c>
+      <c r="M35" s="173" t="s">
         <v>412</v>
       </c>
-      <c r="J35" s="175" t="s">
+      <c r="N35" s="171" t="s">
         <v>413</v>
       </c>
-      <c r="K35" s="175" t="s">
+      <c r="O35" s="171" t="s">
         <v>414</v>
       </c>
-      <c r="L35" s="173" t="s">
-        <v>415</v>
-      </c>
-      <c r="M35" s="173" t="s">
-        <v>416</v>
-      </c>
-      <c r="N35" s="171" t="s">
-        <v>417</v>
-      </c>
-      <c r="O35" s="171" t="s">
-        <v>418</v>
-      </c>
-      <c r="P35" s="203" t="s">
-        <v>408</v>
+      <c r="P35" s="191" t="s">
+        <v>404</v>
       </c>
       <c r="Q35" s="183"/>
       <c r="R35" s="88"/>
@@ -6166,44 +6184,44 @@
       <c r="U35" s="88"/>
     </row>
     <row r="36" spans="1:21" ht="22.5">
-      <c r="A36" s="203"/>
-      <c r="B36" s="204"/>
-      <c r="C36" s="205"/>
-      <c r="D36" s="205"/>
+      <c r="A36" s="191"/>
+      <c r="B36" s="192"/>
+      <c r="C36" s="193"/>
+      <c r="D36" s="193"/>
       <c r="E36" s="181" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F36" s="175" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G36" s="179" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="H36" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I36" s="177" t="s">
+        <v>418</v>
+      </c>
+      <c r="J36" s="175" t="s">
+        <v>321</v>
+      </c>
+      <c r="K36" s="175" t="s">
+        <v>419</v>
+      </c>
+      <c r="L36" s="173" t="s">
+        <v>420</v>
+      </c>
+      <c r="M36" s="173" t="s">
+        <v>421</v>
+      </c>
+      <c r="N36" s="171" t="s">
         <v>422</v>
       </c>
-      <c r="J36" s="175" t="s">
-        <v>325</v>
-      </c>
-      <c r="K36" s="175" t="s">
+      <c r="O36" s="171" t="s">
         <v>423</v>
       </c>
-      <c r="L36" s="173" t="s">
-        <v>424</v>
-      </c>
-      <c r="M36" s="173" t="s">
-        <v>425</v>
-      </c>
-      <c r="N36" s="171" t="s">
-        <v>426</v>
-      </c>
-      <c r="O36" s="171" t="s">
-        <v>427</v>
-      </c>
-      <c r="P36" s="203"/>
+      <c r="P36" s="191"/>
       <c r="Q36" s="183"/>
       <c r="R36" s="88"/>
       <c r="S36" s="88"/>
@@ -6211,44 +6229,44 @@
       <c r="U36" s="88"/>
     </row>
     <row r="37" spans="1:21" ht="22.5">
-      <c r="A37" s="203"/>
-      <c r="B37" s="204"/>
-      <c r="C37" s="205"/>
-      <c r="D37" s="205"/>
+      <c r="A37" s="191"/>
+      <c r="B37" s="192"/>
+      <c r="C37" s="193"/>
+      <c r="D37" s="193"/>
       <c r="E37" s="181" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F37" s="175" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G37" s="179" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="H37" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I37" s="177" t="s">
+        <v>427</v>
+      </c>
+      <c r="J37" s="175" t="s">
+        <v>428</v>
+      </c>
+      <c r="K37" s="175" t="s">
+        <v>220</v>
+      </c>
+      <c r="L37" s="173" t="s">
+        <v>429</v>
+      </c>
+      <c r="M37" s="173" t="s">
+        <v>430</v>
+      </c>
+      <c r="N37" s="171" t="s">
         <v>431</v>
       </c>
-      <c r="J37" s="175" t="s">
+      <c r="O37" s="171" t="s">
         <v>432</v>
       </c>
-      <c r="K37" s="175" t="s">
-        <v>224</v>
-      </c>
-      <c r="L37" s="173" t="s">
-        <v>433</v>
-      </c>
-      <c r="M37" s="173" t="s">
-        <v>434</v>
-      </c>
-      <c r="N37" s="171" t="s">
-        <v>435</v>
-      </c>
-      <c r="O37" s="171" t="s">
-        <v>436</v>
-      </c>
-      <c r="P37" s="203"/>
+      <c r="P37" s="191"/>
       <c r="Q37" s="183"/>
       <c r="R37" s="88"/>
       <c r="S37" s="88"/>
@@ -6256,44 +6274,44 @@
       <c r="U37" s="88"/>
     </row>
     <row r="38" spans="1:21" ht="33.75">
-      <c r="A38" s="203"/>
-      <c r="B38" s="204"/>
-      <c r="C38" s="205"/>
-      <c r="D38" s="205"/>
+      <c r="A38" s="191"/>
+      <c r="B38" s="192"/>
+      <c r="C38" s="193"/>
+      <c r="D38" s="193"/>
       <c r="E38" s="181" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F38" s="175" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G38" s="179" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H38" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I38" s="177" t="s">
+        <v>436</v>
+      </c>
+      <c r="J38" s="175" t="s">
+        <v>437</v>
+      </c>
+      <c r="K38" s="175" t="s">
+        <v>438</v>
+      </c>
+      <c r="L38" s="173" t="s">
+        <v>118</v>
+      </c>
+      <c r="M38" s="173" t="s">
+        <v>439</v>
+      </c>
+      <c r="N38" s="171" t="s">
         <v>440</v>
       </c>
-      <c r="J38" s="175" t="s">
+      <c r="O38" s="171" t="s">
         <v>441</v>
       </c>
-      <c r="K38" s="175" t="s">
-        <v>442</v>
-      </c>
-      <c r="L38" s="173" t="s">
-        <v>122</v>
-      </c>
-      <c r="M38" s="173" t="s">
-        <v>443</v>
-      </c>
-      <c r="N38" s="171" t="s">
-        <v>444</v>
-      </c>
-      <c r="O38" s="171" t="s">
-        <v>445</v>
-      </c>
-      <c r="P38" s="203"/>
+      <c r="P38" s="191"/>
       <c r="Q38" s="183"/>
       <c r="R38" s="88"/>
       <c r="S38" s="88"/>
@@ -6301,44 +6319,44 @@
       <c r="U38" s="88"/>
     </row>
     <row r="39" spans="1:21" ht="22.5">
-      <c r="A39" s="203"/>
-      <c r="B39" s="204"/>
-      <c r="C39" s="205"/>
-      <c r="D39" s="205"/>
+      <c r="A39" s="191"/>
+      <c r="B39" s="192"/>
+      <c r="C39" s="193"/>
+      <c r="D39" s="193"/>
       <c r="E39" s="181" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F39" s="175" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G39" s="179" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H39" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I39" s="177" t="s">
+        <v>445</v>
+      </c>
+      <c r="J39" s="175" t="s">
+        <v>446</v>
+      </c>
+      <c r="K39" s="175" t="s">
+        <v>447</v>
+      </c>
+      <c r="L39" s="173" t="s">
+        <v>448</v>
+      </c>
+      <c r="M39" s="173" t="s">
         <v>449</v>
       </c>
-      <c r="J39" s="175" t="s">
+      <c r="N39" s="171" t="s">
         <v>450</v>
       </c>
-      <c r="K39" s="175" t="s">
+      <c r="O39" s="171" t="s">
         <v>451</v>
       </c>
-      <c r="L39" s="173" t="s">
-        <v>452</v>
-      </c>
-      <c r="M39" s="173" t="s">
-        <v>453</v>
-      </c>
-      <c r="N39" s="171" t="s">
-        <v>454</v>
-      </c>
-      <c r="O39" s="171" t="s">
-        <v>455</v>
-      </c>
-      <c r="P39" s="203"/>
+      <c r="P39" s="191"/>
       <c r="Q39" s="183"/>
       <c r="R39" s="88"/>
       <c r="S39" s="88"/>
@@ -6350,49 +6368,49 @@
         <v>53</v>
       </c>
       <c r="B40" s="188" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C40" s="186" t="s">
+        <v>452</v>
+      </c>
+      <c r="D40" s="186" t="s">
+        <v>453</v>
+      </c>
+      <c r="E40" s="180" t="s">
+        <v>455</v>
+      </c>
+      <c r="F40" s="174" t="s">
         <v>456</v>
       </c>
-      <c r="D40" s="186" t="s">
+      <c r="G40" s="178" t="s">
         <v>457</v>
-      </c>
-      <c r="E40" s="180" t="s">
-        <v>459</v>
-      </c>
-      <c r="F40" s="174" t="s">
-        <v>460</v>
-      </c>
-      <c r="G40" s="178" t="s">
-        <v>461</v>
       </c>
       <c r="H40" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I40" s="176" t="s">
+        <v>458</v>
+      </c>
+      <c r="J40" s="174" t="s">
+        <v>459</v>
+      </c>
+      <c r="K40" s="174" t="s">
+        <v>460</v>
+      </c>
+      <c r="L40" s="172" t="s">
+        <v>461</v>
+      </c>
+      <c r="M40" s="172" t="s">
         <v>462</v>
       </c>
-      <c r="J40" s="174" t="s">
+      <c r="N40" s="170" t="s">
         <v>463</v>
       </c>
-      <c r="K40" s="174" t="s">
+      <c r="O40" s="170" t="s">
         <v>464</v>
       </c>
-      <c r="L40" s="172" t="s">
-        <v>465</v>
-      </c>
-      <c r="M40" s="172" t="s">
-        <v>466</v>
-      </c>
-      <c r="N40" s="170" t="s">
-        <v>467</v>
-      </c>
-      <c r="O40" s="170" t="s">
-        <v>468</v>
-      </c>
       <c r="P40" s="168" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="Q40" s="183"/>
       <c r="R40" s="88"/>
@@ -6401,53 +6419,53 @@
       <c r="U40" s="88"/>
     </row>
     <row r="41" spans="1:21" ht="22.5">
-      <c r="A41" s="203" t="s">
+      <c r="A41" s="191" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="204" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" s="205" t="s">
+      <c r="B41" s="192" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="193" t="s">
+        <v>465</v>
+      </c>
+      <c r="D41" s="193" t="s">
+        <v>466</v>
+      </c>
+      <c r="E41" s="181" t="s">
+        <v>468</v>
+      </c>
+      <c r="F41" s="175" t="s">
         <v>469</v>
       </c>
-      <c r="D41" s="205" t="s">
+      <c r="G41" s="179" t="s">
         <v>470</v>
-      </c>
-      <c r="E41" s="181" t="s">
-        <v>472</v>
-      </c>
-      <c r="F41" s="175" t="s">
-        <v>473</v>
-      </c>
-      <c r="G41" s="179" t="s">
-        <v>474</v>
       </c>
       <c r="H41" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I41" s="177" t="s">
+        <v>471</v>
+      </c>
+      <c r="J41" s="175" t="s">
+        <v>472</v>
+      </c>
+      <c r="K41" s="175" t="s">
+        <v>473</v>
+      </c>
+      <c r="L41" s="173" t="s">
+        <v>418</v>
+      </c>
+      <c r="M41" s="173" t="s">
+        <v>474</v>
+      </c>
+      <c r="N41" s="171" t="s">
         <v>475</v>
       </c>
-      <c r="J41" s="175" t="s">
+      <c r="O41" s="171" t="s">
         <v>476</v>
       </c>
-      <c r="K41" s="175" t="s">
-        <v>477</v>
-      </c>
-      <c r="L41" s="173" t="s">
-        <v>422</v>
-      </c>
-      <c r="M41" s="173" t="s">
-        <v>478</v>
-      </c>
-      <c r="N41" s="171" t="s">
-        <v>479</v>
-      </c>
-      <c r="O41" s="171" t="s">
-        <v>480</v>
-      </c>
-      <c r="P41" s="203" t="s">
-        <v>471</v>
+      <c r="P41" s="191" t="s">
+        <v>467</v>
       </c>
       <c r="Q41" s="183"/>
       <c r="R41" s="88"/>
@@ -6456,38 +6474,38 @@
       <c r="U41" s="88"/>
     </row>
     <row r="42" spans="1:21" ht="22.5">
-      <c r="A42" s="203"/>
-      <c r="B42" s="204"/>
-      <c r="C42" s="205"/>
-      <c r="D42" s="205"/>
+      <c r="A42" s="191"/>
+      <c r="B42" s="192"/>
+      <c r="C42" s="193"/>
+      <c r="D42" s="193"/>
       <c r="E42" s="181" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F42" s="175" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G42" s="179" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="H42" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I42" s="177" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="J42" s="175" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="K42" s="175"/>
       <c r="L42" s="173" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="M42" s="173"/>
       <c r="N42" s="171" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="O42" s="171"/>
-      <c r="P42" s="203"/>
+      <c r="P42" s="191"/>
       <c r="Q42" s="183"/>
       <c r="R42" s="88"/>
       <c r="S42" s="88"/>
@@ -6495,44 +6513,44 @@
       <c r="U42" s="88"/>
     </row>
     <row r="43" spans="1:21" ht="22.5">
-      <c r="A43" s="203"/>
-      <c r="B43" s="204"/>
-      <c r="C43" s="205"/>
-      <c r="D43" s="205"/>
+      <c r="A43" s="191"/>
+      <c r="B43" s="192"/>
+      <c r="C43" s="193"/>
+      <c r="D43" s="193"/>
       <c r="E43" s="181" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F43" s="175" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G43" s="179" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="H43" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I43" s="177" t="s">
+        <v>486</v>
+      </c>
+      <c r="J43" s="175" t="s">
+        <v>487</v>
+      </c>
+      <c r="K43" s="175" t="s">
+        <v>256</v>
+      </c>
+      <c r="L43" s="173" t="s">
+        <v>488</v>
+      </c>
+      <c r="M43" s="173" t="s">
+        <v>489</v>
+      </c>
+      <c r="N43" s="171" t="s">
         <v>490</v>
       </c>
-      <c r="J43" s="175" t="s">
+      <c r="O43" s="171" t="s">
         <v>491</v>
       </c>
-      <c r="K43" s="175" t="s">
-        <v>260</v>
-      </c>
-      <c r="L43" s="173" t="s">
-        <v>492</v>
-      </c>
-      <c r="M43" s="173" t="s">
-        <v>493</v>
-      </c>
-      <c r="N43" s="171" t="s">
-        <v>494</v>
-      </c>
-      <c r="O43" s="171" t="s">
-        <v>495</v>
-      </c>
-      <c r="P43" s="203"/>
+      <c r="P43" s="191"/>
       <c r="Q43" s="183"/>
       <c r="R43" s="88"/>
       <c r="S43" s="88"/>
@@ -6540,53 +6558,53 @@
       <c r="U43" s="88"/>
     </row>
     <row r="44" spans="1:21" ht="22.5">
-      <c r="A44" s="206" t="s">
+      <c r="A44" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="207" t="s">
+      <c r="B44" s="195" t="s">
         <v>76</v>
       </c>
-      <c r="C44" s="208" t="s">
+      <c r="C44" s="196" t="s">
+        <v>492</v>
+      </c>
+      <c r="D44" s="196" t="s">
+        <v>493</v>
+      </c>
+      <c r="E44" s="180" t="s">
+        <v>494</v>
+      </c>
+      <c r="F44" s="174" t="s">
+        <v>495</v>
+      </c>
+      <c r="G44" s="178" t="s">
         <v>496</v>
       </c>
-      <c r="D44" s="208" t="s">
+      <c r="H44" s="174" t="s">
+        <v>129</v>
+      </c>
+      <c r="I44" s="176" t="s">
         <v>497</v>
       </c>
-      <c r="E44" s="180" t="s">
+      <c r="J44" s="174" t="s">
         <v>498</v>
       </c>
-      <c r="F44" s="174" t="s">
+      <c r="K44" s="174" t="s">
         <v>499</v>
       </c>
-      <c r="G44" s="178" t="s">
+      <c r="L44" s="172" t="s">
         <v>500</v>
       </c>
-      <c r="H44" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="I44" s="176" t="s">
+      <c r="M44" s="172" t="s">
         <v>501</v>
       </c>
-      <c r="J44" s="174" t="s">
+      <c r="N44" s="170" t="s">
         <v>502</v>
       </c>
-      <c r="K44" s="174" t="s">
+      <c r="O44" s="170" t="s">
         <v>503</v>
       </c>
-      <c r="L44" s="172" t="s">
-        <v>504</v>
-      </c>
-      <c r="M44" s="172" t="s">
-        <v>505</v>
-      </c>
-      <c r="N44" s="170" t="s">
-        <v>506</v>
-      </c>
-      <c r="O44" s="170" t="s">
-        <v>507</v>
-      </c>
-      <c r="P44" s="206" t="s">
-        <v>471</v>
+      <c r="P44" s="194" t="s">
+        <v>467</v>
       </c>
       <c r="Q44" s="183"/>
       <c r="R44" s="88"/>
@@ -6595,44 +6613,44 @@
       <c r="U44" s="88"/>
     </row>
     <row r="45" spans="1:21" ht="22.5">
-      <c r="A45" s="206"/>
-      <c r="B45" s="207"/>
-      <c r="C45" s="208"/>
-      <c r="D45" s="208"/>
+      <c r="A45" s="194"/>
+      <c r="B45" s="195"/>
+      <c r="C45" s="196"/>
+      <c r="D45" s="196"/>
       <c r="E45" s="180" t="s">
+        <v>504</v>
+      </c>
+      <c r="F45" s="174" t="s">
+        <v>505</v>
+      </c>
+      <c r="G45" s="178" t="s">
+        <v>506</v>
+      </c>
+      <c r="H45" s="174" t="s">
+        <v>129</v>
+      </c>
+      <c r="I45" s="176" t="s">
+        <v>507</v>
+      </c>
+      <c r="J45" s="174" t="s">
         <v>508</v>
       </c>
-      <c r="F45" s="174" t="s">
+      <c r="K45" s="174" t="s">
         <v>509</v>
       </c>
-      <c r="G45" s="178" t="s">
+      <c r="L45" s="172" t="s">
         <v>510</v>
       </c>
-      <c r="H45" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="I45" s="176" t="s">
+      <c r="M45" s="172" t="s">
         <v>511</v>
       </c>
-      <c r="J45" s="174" t="s">
+      <c r="N45" s="170" t="s">
         <v>512</v>
       </c>
-      <c r="K45" s="174" t="s">
-        <v>513</v>
-      </c>
-      <c r="L45" s="172" t="s">
-        <v>514</v>
-      </c>
-      <c r="M45" s="172" t="s">
-        <v>515</v>
-      </c>
-      <c r="N45" s="170" t="s">
-        <v>516</v>
-      </c>
       <c r="O45" s="170" t="s">
-        <v>494</v>
-      </c>
-      <c r="P45" s="206"/>
+        <v>490</v>
+      </c>
+      <c r="P45" s="194"/>
       <c r="Q45" s="183"/>
       <c r="R45" s="88"/>
       <c r="S45" s="88"/>
@@ -6640,44 +6658,44 @@
       <c r="U45" s="88"/>
     </row>
     <row r="46" spans="1:21" ht="22.5">
-      <c r="A46" s="206"/>
-      <c r="B46" s="207"/>
-      <c r="C46" s="208"/>
-      <c r="D46" s="208"/>
+      <c r="A46" s="194"/>
+      <c r="B46" s="195"/>
+      <c r="C46" s="196"/>
+      <c r="D46" s="196"/>
       <c r="E46" s="180" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F46" s="174" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G46" s="178" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="H46" s="174" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I46" s="176" t="s">
         <v>94</v>
       </c>
       <c r="J46" s="174" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K46" s="174" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="L46" s="172" t="s">
         <v>98</v>
       </c>
       <c r="M46" s="172" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N46" s="170" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="O46" s="170" t="s">
-        <v>512</v>
-      </c>
-      <c r="P46" s="206"/>
+        <v>508</v>
+      </c>
+      <c r="P46" s="194"/>
       <c r="Q46" s="183"/>
       <c r="R46" s="88"/>
       <c r="S46" s="88"/>
@@ -6685,53 +6703,53 @@
       <c r="U46" s="88"/>
     </row>
     <row r="47" spans="1:21" ht="67.5">
-      <c r="A47" s="203" t="s">
+      <c r="A47" s="191" t="s">
         <v>61</v>
       </c>
-      <c r="B47" s="204" t="s">
+      <c r="B47" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="205" t="s">
+      <c r="C47" s="193" t="s">
+        <v>518</v>
+      </c>
+      <c r="D47" s="193" t="s">
+        <v>519</v>
+      </c>
+      <c r="E47" s="181" t="s">
+        <v>521</v>
+      </c>
+      <c r="F47" s="175" t="s">
         <v>522</v>
       </c>
-      <c r="D47" s="205" t="s">
+      <c r="G47" s="179" t="s">
         <v>523</v>
-      </c>
-      <c r="E47" s="181" t="s">
-        <v>525</v>
-      </c>
-      <c r="F47" s="175" t="s">
-        <v>526</v>
-      </c>
-      <c r="G47" s="179" t="s">
-        <v>527</v>
       </c>
       <c r="H47" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I47" s="177" t="s">
+        <v>524</v>
+      </c>
+      <c r="J47" s="175" t="s">
+        <v>341</v>
+      </c>
+      <c r="K47" s="175" t="s">
+        <v>525</v>
+      </c>
+      <c r="L47" s="173" t="s">
+        <v>526</v>
+      </c>
+      <c r="M47" s="173" t="s">
+        <v>527</v>
+      </c>
+      <c r="N47" s="171" t="s">
         <v>528</v>
       </c>
-      <c r="J47" s="175" t="s">
-        <v>345</v>
-      </c>
-      <c r="K47" s="175" t="s">
+      <c r="O47" s="171" t="s">
         <v>529</v>
       </c>
-      <c r="L47" s="173" t="s">
-        <v>530</v>
-      </c>
-      <c r="M47" s="173" t="s">
-        <v>531</v>
-      </c>
-      <c r="N47" s="171" t="s">
-        <v>532</v>
-      </c>
-      <c r="O47" s="171" t="s">
-        <v>533</v>
-      </c>
-      <c r="P47" s="203" t="s">
-        <v>524</v>
+      <c r="P47" s="191" t="s">
+        <v>520</v>
       </c>
       <c r="Q47" s="183"/>
       <c r="R47" s="88"/>
@@ -6740,44 +6758,44 @@
       <c r="U47" s="88"/>
     </row>
     <row r="48" spans="1:21" ht="33.75">
-      <c r="A48" s="203"/>
-      <c r="B48" s="204"/>
-      <c r="C48" s="205"/>
-      <c r="D48" s="205"/>
+      <c r="A48" s="191"/>
+      <c r="B48" s="192"/>
+      <c r="C48" s="193"/>
+      <c r="D48" s="193"/>
       <c r="E48" s="181" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F48" s="175" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="G48" s="179" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H48" s="175" t="s">
         <v>83</v>
       </c>
       <c r="I48" s="177" t="s">
+        <v>533</v>
+      </c>
+      <c r="J48" s="175" t="s">
+        <v>534</v>
+      </c>
+      <c r="K48" s="175" t="s">
+        <v>535</v>
+      </c>
+      <c r="L48" s="173" t="s">
+        <v>536</v>
+      </c>
+      <c r="M48" s="173" t="s">
         <v>537</v>
       </c>
-      <c r="J48" s="175" t="s">
+      <c r="N48" s="171" t="s">
         <v>538</v>
       </c>
-      <c r="K48" s="175" t="s">
+      <c r="O48" s="171" t="s">
         <v>539</v>
       </c>
-      <c r="L48" s="173" t="s">
-        <v>540</v>
-      </c>
-      <c r="M48" s="173" t="s">
-        <v>541</v>
-      </c>
-      <c r="N48" s="171" t="s">
-        <v>542</v>
-      </c>
-      <c r="O48" s="171" t="s">
-        <v>543</v>
-      </c>
-      <c r="P48" s="203"/>
+      <c r="P48" s="191"/>
       <c r="Q48" s="183"/>
       <c r="R48" s="88"/>
       <c r="S48" s="88"/>
@@ -6785,53 +6803,53 @@
       <c r="U48" s="88"/>
     </row>
     <row r="49" spans="1:21" ht="90">
-      <c r="A49" s="206" t="s">
+      <c r="A49" s="194" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="207" t="s">
-        <v>126</v>
-      </c>
-      <c r="C49" s="208" t="s">
+      <c r="B49" s="195" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="196" t="s">
+        <v>540</v>
+      </c>
+      <c r="D49" s="196" t="s">
+        <v>541</v>
+      </c>
+      <c r="E49" s="180" t="s">
+        <v>543</v>
+      </c>
+      <c r="F49" s="174" t="s">
         <v>544</v>
       </c>
-      <c r="D49" s="208" t="s">
+      <c r="G49" s="178" t="s">
         <v>545</v>
-      </c>
-      <c r="E49" s="180" t="s">
-        <v>547</v>
-      </c>
-      <c r="F49" s="174" t="s">
-        <v>548</v>
-      </c>
-      <c r="G49" s="178" t="s">
-        <v>549</v>
       </c>
       <c r="H49" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I49" s="176" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J49" s="174" t="s">
+        <v>546</v>
+      </c>
+      <c r="K49" s="174" t="s">
+        <v>547</v>
+      </c>
+      <c r="L49" s="172" t="s">
+        <v>548</v>
+      </c>
+      <c r="M49" s="172" t="s">
+        <v>549</v>
+      </c>
+      <c r="N49" s="170" t="s">
         <v>550</v>
       </c>
-      <c r="K49" s="174" t="s">
+      <c r="O49" s="170" t="s">
         <v>551</v>
       </c>
-      <c r="L49" s="172" t="s">
-        <v>552</v>
-      </c>
-      <c r="M49" s="172" t="s">
-        <v>553</v>
-      </c>
-      <c r="N49" s="170" t="s">
-        <v>554</v>
-      </c>
-      <c r="O49" s="170" t="s">
-        <v>555</v>
-      </c>
-      <c r="P49" s="206" t="s">
-        <v>546</v>
+      <c r="P49" s="194" t="s">
+        <v>542</v>
       </c>
       <c r="Q49" s="183"/>
       <c r="R49" s="88"/>
@@ -6840,44 +6858,44 @@
       <c r="U49" s="88"/>
     </row>
     <row r="50" spans="1:21" ht="33.75">
-      <c r="A50" s="206"/>
-      <c r="B50" s="207"/>
-      <c r="C50" s="208"/>
-      <c r="D50" s="208"/>
+      <c r="A50" s="194"/>
+      <c r="B50" s="195"/>
+      <c r="C50" s="196"/>
+      <c r="D50" s="196"/>
       <c r="E50" s="180" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F50" s="174" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="G50" s="178" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H50" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I50" s="176" t="s">
+        <v>555</v>
+      </c>
+      <c r="J50" s="174" t="s">
+        <v>210</v>
+      </c>
+      <c r="K50" s="174" t="s">
+        <v>556</v>
+      </c>
+      <c r="L50" s="172" t="s">
+        <v>557</v>
+      </c>
+      <c r="M50" s="172" t="s">
+        <v>558</v>
+      </c>
+      <c r="N50" s="170" t="s">
         <v>559</v>
       </c>
-      <c r="J50" s="174" t="s">
-        <v>214</v>
-      </c>
-      <c r="K50" s="174" t="s">
+      <c r="O50" s="170" t="s">
         <v>560</v>
       </c>
-      <c r="L50" s="172" t="s">
-        <v>561</v>
-      </c>
-      <c r="M50" s="172" t="s">
-        <v>562</v>
-      </c>
-      <c r="N50" s="170" t="s">
-        <v>563</v>
-      </c>
-      <c r="O50" s="170" t="s">
-        <v>564</v>
-      </c>
-      <c r="P50" s="206"/>
+      <c r="P50" s="194"/>
       <c r="Q50" s="183"/>
       <c r="R50" s="88"/>
       <c r="S50" s="88"/>
@@ -6892,46 +6910,46 @@
         <v>76</v>
       </c>
       <c r="C51" s="187" t="s">
+        <v>561</v>
+      </c>
+      <c r="D51" s="187" t="s">
+        <v>562</v>
+      </c>
+      <c r="E51" s="181" t="s">
+        <v>564</v>
+      </c>
+      <c r="F51" s="175" t="s">
         <v>565</v>
       </c>
-      <c r="D51" s="187" t="s">
+      <c r="G51" s="179" t="s">
         <v>566</v>
       </c>
-      <c r="E51" s="181" t="s">
+      <c r="H51" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I51" s="177" t="s">
+        <v>567</v>
+      </c>
+      <c r="J51" s="175" t="s">
         <v>568</v>
       </c>
-      <c r="F51" s="175" t="s">
+      <c r="K51" s="175" t="s">
         <v>569</v>
       </c>
-      <c r="G51" s="179" t="s">
+      <c r="L51" s="173" t="s">
         <v>570</v>
       </c>
-      <c r="H51" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I51" s="177" t="s">
+      <c r="M51" s="173" t="s">
         <v>571</v>
       </c>
-      <c r="J51" s="175" t="s">
+      <c r="N51" s="171" t="s">
         <v>572</v>
       </c>
-      <c r="K51" s="175" t="s">
+      <c r="O51" s="171" t="s">
         <v>573</v>
       </c>
-      <c r="L51" s="173" t="s">
-        <v>574</v>
-      </c>
-      <c r="M51" s="173" t="s">
-        <v>575</v>
-      </c>
-      <c r="N51" s="171" t="s">
-        <v>576</v>
-      </c>
-      <c r="O51" s="171" t="s">
-        <v>577</v>
-      </c>
       <c r="P51" s="169" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="Q51" s="183"/>
       <c r="R51" s="88"/>
@@ -6940,53 +6958,53 @@
       <c r="U51" s="88"/>
     </row>
     <row r="52" spans="1:21" ht="22.5">
-      <c r="A52" s="206" t="s">
+      <c r="A52" s="194" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="207" t="s">
+      <c r="B52" s="195" t="s">
         <v>76</v>
       </c>
-      <c r="C52" s="208" t="s">
+      <c r="C52" s="196" t="s">
+        <v>574</v>
+      </c>
+      <c r="D52" s="196" t="s">
+        <v>575</v>
+      </c>
+      <c r="E52" s="167" t="s">
+        <v>577</v>
+      </c>
+      <c r="F52" s="174" t="s">
         <v>578</v>
       </c>
-      <c r="D52" s="208" t="s">
+      <c r="G52" s="178" t="s">
         <v>579</v>
       </c>
-      <c r="E52" s="167" t="s">
+      <c r="H52" s="174" t="s">
+        <v>129</v>
+      </c>
+      <c r="I52" s="176" t="s">
+        <v>580</v>
+      </c>
+      <c r="J52" s="174" t="s">
         <v>581</v>
       </c>
-      <c r="F52" s="174" t="s">
+      <c r="K52" s="174" t="s">
         <v>582</v>
       </c>
-      <c r="G52" s="178" t="s">
+      <c r="L52" s="172" t="s">
         <v>583</v>
       </c>
-      <c r="H52" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="I52" s="176" t="s">
+      <c r="M52" s="172" t="s">
         <v>584</v>
       </c>
-      <c r="J52" s="174" t="s">
+      <c r="N52" s="170" t="s">
         <v>585</v>
       </c>
-      <c r="K52" s="174" t="s">
-        <v>586</v>
-      </c>
-      <c r="L52" s="172" t="s">
-        <v>587</v>
-      </c>
-      <c r="M52" s="172" t="s">
-        <v>588</v>
-      </c>
-      <c r="N52" s="170" t="s">
-        <v>589</v>
-      </c>
       <c r="O52" s="170" t="s">
-        <v>502</v>
-      </c>
-      <c r="P52" s="206" t="s">
-        <v>580</v>
+        <v>498</v>
+      </c>
+      <c r="P52" s="194" t="s">
+        <v>576</v>
       </c>
       <c r="Q52" s="183"/>
       <c r="R52" s="88"/>
@@ -6995,44 +7013,44 @@
       <c r="U52" s="88"/>
     </row>
     <row r="53" spans="1:21" ht="22.5">
-      <c r="A53" s="206"/>
-      <c r="B53" s="207"/>
-      <c r="C53" s="208"/>
-      <c r="D53" s="208"/>
+      <c r="A53" s="194"/>
+      <c r="B53" s="195"/>
+      <c r="C53" s="196"/>
+      <c r="D53" s="196"/>
       <c r="E53" s="180" t="s">
+        <v>586</v>
+      </c>
+      <c r="F53" s="174" t="s">
+        <v>587</v>
+      </c>
+      <c r="G53" s="178" t="s">
+        <v>579</v>
+      </c>
+      <c r="H53" s="174" t="s">
+        <v>129</v>
+      </c>
+      <c r="I53" s="176" t="s">
+        <v>588</v>
+      </c>
+      <c r="J53" s="174" t="s">
+        <v>581</v>
+      </c>
+      <c r="K53" s="174" t="s">
+        <v>582</v>
+      </c>
+      <c r="L53" s="172" t="s">
+        <v>583</v>
+      </c>
+      <c r="M53" s="172" t="s">
+        <v>584</v>
+      </c>
+      <c r="N53" s="170" t="s">
+        <v>589</v>
+      </c>
+      <c r="O53" s="170" t="s">
         <v>590</v>
       </c>
-      <c r="F53" s="174" t="s">
-        <v>591</v>
-      </c>
-      <c r="G53" s="178" t="s">
-        <v>583</v>
-      </c>
-      <c r="H53" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="I53" s="176" t="s">
-        <v>592</v>
-      </c>
-      <c r="J53" s="174" t="s">
-        <v>585</v>
-      </c>
-      <c r="K53" s="174" t="s">
-        <v>586</v>
-      </c>
-      <c r="L53" s="172" t="s">
-        <v>587</v>
-      </c>
-      <c r="M53" s="172" t="s">
-        <v>588</v>
-      </c>
-      <c r="N53" s="170" t="s">
-        <v>593</v>
-      </c>
-      <c r="O53" s="170" t="s">
-        <v>594</v>
-      </c>
-      <c r="P53" s="206"/>
+      <c r="P53" s="194"/>
       <c r="Q53" s="183"/>
       <c r="R53" s="88"/>
       <c r="S53" s="88"/>
@@ -7040,53 +7058,53 @@
       <c r="U53" s="88"/>
     </row>
     <row r="54" spans="1:21" ht="22.5">
-      <c r="A54" s="203" t="s">
+      <c r="A54" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="B54" s="204" t="s">
+      <c r="B54" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="205" t="s">
+      <c r="C54" s="193" t="s">
+        <v>591</v>
+      </c>
+      <c r="D54" s="193" t="s">
+        <v>592</v>
+      </c>
+      <c r="E54" s="181" t="s">
+        <v>593</v>
+      </c>
+      <c r="F54" s="175" t="s">
+        <v>594</v>
+      </c>
+      <c r="G54" s="179" t="s">
         <v>595</v>
       </c>
-      <c r="D54" s="205" t="s">
+      <c r="H54" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I54" s="177" t="s">
         <v>596</v>
       </c>
-      <c r="E54" s="181" t="s">
+      <c r="J54" s="175" t="s">
         <v>597</v>
       </c>
-      <c r="F54" s="175" t="s">
+      <c r="K54" s="175" t="s">
         <v>598</v>
       </c>
-      <c r="G54" s="179" t="s">
+      <c r="L54" s="173" t="s">
         <v>599</v>
       </c>
-      <c r="H54" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I54" s="177" t="s">
+      <c r="M54" s="173" t="s">
         <v>600</v>
       </c>
-      <c r="J54" s="175" t="s">
+      <c r="N54" s="171" t="s">
+        <v>280</v>
+      </c>
+      <c r="O54" s="171" t="s">
         <v>601</v>
       </c>
-      <c r="K54" s="175" t="s">
-        <v>602</v>
-      </c>
-      <c r="L54" s="173" t="s">
-        <v>603</v>
-      </c>
-      <c r="M54" s="173" t="s">
-        <v>604</v>
-      </c>
-      <c r="N54" s="171" t="s">
-        <v>284</v>
-      </c>
-      <c r="O54" s="171" t="s">
-        <v>605</v>
-      </c>
-      <c r="P54" s="203" t="s">
-        <v>567</v>
+      <c r="P54" s="191" t="s">
+        <v>563</v>
       </c>
       <c r="Q54" s="183"/>
       <c r="R54" s="88"/>
@@ -7095,44 +7113,44 @@
       <c r="U54" s="88"/>
     </row>
     <row r="55" spans="1:21" ht="22.5">
-      <c r="A55" s="203"/>
-      <c r="B55" s="204"/>
-      <c r="C55" s="205"/>
-      <c r="D55" s="205"/>
+      <c r="A55" s="191"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
       <c r="E55" s="181" t="s">
+        <v>602</v>
+      </c>
+      <c r="F55" s="175" t="s">
+        <v>603</v>
+      </c>
+      <c r="G55" s="179" t="s">
+        <v>604</v>
+      </c>
+      <c r="H55" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I55" s="177" t="s">
+        <v>605</v>
+      </c>
+      <c r="J55" s="175" t="s">
         <v>606</v>
       </c>
-      <c r="F55" s="175" t="s">
+      <c r="K55" s="175" t="s">
         <v>607</v>
       </c>
-      <c r="G55" s="179" t="s">
+      <c r="L55" s="173" t="s">
         <v>608</v>
       </c>
-      <c r="H55" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I55" s="177" t="s">
+      <c r="M55" s="173" t="s">
+        <v>445</v>
+      </c>
+      <c r="N55" s="171" t="s">
         <v>609</v>
       </c>
-      <c r="J55" s="175" t="s">
+      <c r="O55" s="171" t="s">
         <v>610</v>
       </c>
-      <c r="K55" s="175" t="s">
-        <v>611</v>
-      </c>
-      <c r="L55" s="173" t="s">
-        <v>612</v>
-      </c>
-      <c r="M55" s="173" t="s">
-        <v>449</v>
-      </c>
-      <c r="N55" s="171" t="s">
-        <v>613</v>
-      </c>
-      <c r="O55" s="171" t="s">
-        <v>614</v>
-      </c>
-      <c r="P55" s="203"/>
+      <c r="P55" s="191"/>
       <c r="Q55" s="183"/>
       <c r="R55" s="88"/>
       <c r="S55" s="88"/>
@@ -7140,44 +7158,44 @@
       <c r="U55" s="88"/>
     </row>
     <row r="56" spans="1:21" ht="22.5">
-      <c r="A56" s="203"/>
-      <c r="B56" s="204"/>
-      <c r="C56" s="205"/>
-      <c r="D56" s="205"/>
+      <c r="A56" s="191"/>
+      <c r="B56" s="192"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="193"/>
       <c r="E56" s="181" t="s">
+        <v>611</v>
+      </c>
+      <c r="F56" s="175" t="s">
+        <v>612</v>
+      </c>
+      <c r="G56" s="179" t="s">
+        <v>613</v>
+      </c>
+      <c r="H56" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I56" s="177" t="s">
+        <v>241</v>
+      </c>
+      <c r="J56" s="175" t="s">
+        <v>614</v>
+      </c>
+      <c r="K56" s="175" t="s">
         <v>615</v>
       </c>
-      <c r="F56" s="175" t="s">
+      <c r="L56" s="173" t="s">
+        <v>299</v>
+      </c>
+      <c r="M56" s="173" t="s">
+        <v>164</v>
+      </c>
+      <c r="N56" s="171" t="s">
+        <v>108</v>
+      </c>
+      <c r="O56" s="171" t="s">
         <v>616</v>
       </c>
-      <c r="G56" s="179" t="s">
-        <v>617</v>
-      </c>
-      <c r="H56" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I56" s="177" t="s">
-        <v>245</v>
-      </c>
-      <c r="J56" s="175" t="s">
-        <v>618</v>
-      </c>
-      <c r="K56" s="175" t="s">
-        <v>619</v>
-      </c>
-      <c r="L56" s="173" t="s">
-        <v>303</v>
-      </c>
-      <c r="M56" s="173" t="s">
-        <v>168</v>
-      </c>
-      <c r="N56" s="171" t="s">
-        <v>112</v>
-      </c>
-      <c r="O56" s="171" t="s">
-        <v>620</v>
-      </c>
-      <c r="P56" s="203"/>
+      <c r="P56" s="191"/>
       <c r="Q56" s="183"/>
       <c r="R56" s="88"/>
       <c r="S56" s="88"/>
@@ -7185,44 +7203,44 @@
       <c r="U56" s="88"/>
     </row>
     <row r="57" spans="1:21" ht="22.5">
-      <c r="A57" s="203"/>
-      <c r="B57" s="204"/>
-      <c r="C57" s="205"/>
-      <c r="D57" s="205"/>
+      <c r="A57" s="191"/>
+      <c r="B57" s="192"/>
+      <c r="C57" s="193"/>
+      <c r="D57" s="193"/>
       <c r="E57" s="181" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F57" s="175" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="G57" s="179" t="s">
+        <v>595</v>
+      </c>
+      <c r="H57" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I57" s="177" t="s">
+        <v>619</v>
+      </c>
+      <c r="J57" s="175" t="s">
+        <v>597</v>
+      </c>
+      <c r="K57" s="175" t="s">
+        <v>598</v>
+      </c>
+      <c r="L57" s="173" t="s">
         <v>599</v>
       </c>
-      <c r="H57" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I57" s="177" t="s">
-        <v>623</v>
-      </c>
-      <c r="J57" s="175" t="s">
-        <v>601</v>
-      </c>
-      <c r="K57" s="175" t="s">
-        <v>602</v>
-      </c>
-      <c r="L57" s="173" t="s">
-        <v>603</v>
-      </c>
       <c r="M57" s="173" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="N57" s="171" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="O57" s="171" t="s">
-        <v>503</v>
-      </c>
-      <c r="P57" s="203"/>
+        <v>499</v>
+      </c>
+      <c r="P57" s="191"/>
       <c r="Q57" s="183"/>
       <c r="R57" s="88"/>
       <c r="S57" s="88"/>
@@ -7230,44 +7248,44 @@
       <c r="U57" s="88"/>
     </row>
     <row r="58" spans="1:21" ht="22.5">
-      <c r="A58" s="203"/>
-      <c r="B58" s="204"/>
-      <c r="C58" s="205"/>
-      <c r="D58" s="205"/>
+      <c r="A58" s="191"/>
+      <c r="B58" s="192"/>
+      <c r="C58" s="193"/>
+      <c r="D58" s="193"/>
       <c r="E58" s="181" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="F58" s="175" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G58" s="179" t="s">
+        <v>604</v>
+      </c>
+      <c r="H58" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I58" s="177" t="s">
+        <v>622</v>
+      </c>
+      <c r="J58" s="175" t="s">
+        <v>606</v>
+      </c>
+      <c r="K58" s="175" t="s">
+        <v>607</v>
+      </c>
+      <c r="L58" s="173" t="s">
         <v>608</v>
       </c>
-      <c r="H58" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I58" s="177" t="s">
-        <v>626</v>
-      </c>
-      <c r="J58" s="175" t="s">
-        <v>610</v>
-      </c>
-      <c r="K58" s="175" t="s">
-        <v>611</v>
-      </c>
-      <c r="L58" s="173" t="s">
-        <v>612</v>
-      </c>
       <c r="M58" s="173" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="N58" s="171" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="O58" s="171" t="s">
-        <v>307</v>
-      </c>
-      <c r="P58" s="203"/>
+        <v>303</v>
+      </c>
+      <c r="P58" s="191"/>
       <c r="Q58" s="183"/>
       <c r="R58" s="88"/>
       <c r="S58" s="88"/>
@@ -7275,44 +7293,44 @@
       <c r="U58" s="88"/>
     </row>
     <row r="59" spans="1:21" ht="22.5">
-      <c r="A59" s="203"/>
-      <c r="B59" s="204"/>
-      <c r="C59" s="205"/>
-      <c r="D59" s="205"/>
+      <c r="A59" s="191"/>
+      <c r="B59" s="192"/>
+      <c r="C59" s="193"/>
+      <c r="D59" s="193"/>
       <c r="E59" s="181" t="s">
+        <v>624</v>
+      </c>
+      <c r="F59" s="175" t="s">
+        <v>625</v>
+      </c>
+      <c r="G59" s="179" t="s">
+        <v>626</v>
+      </c>
+      <c r="H59" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I59" s="177" t="s">
+        <v>627</v>
+      </c>
+      <c r="J59" s="175" t="s">
         <v>628</v>
       </c>
-      <c r="F59" s="175" t="s">
+      <c r="K59" s="175" t="s">
         <v>629</v>
       </c>
-      <c r="G59" s="179" t="s">
+      <c r="L59" s="173" t="s">
         <v>630</v>
       </c>
-      <c r="H59" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I59" s="177" t="s">
+      <c r="M59" s="173" t="s">
         <v>631</v>
       </c>
-      <c r="J59" s="175" t="s">
-        <v>632</v>
-      </c>
-      <c r="K59" s="175" t="s">
-        <v>633</v>
-      </c>
-      <c r="L59" s="173" t="s">
-        <v>634</v>
-      </c>
-      <c r="M59" s="173" t="s">
-        <v>635</v>
-      </c>
       <c r="N59" s="171" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="O59" s="171" t="s">
-        <v>124</v>
-      </c>
-      <c r="P59" s="203"/>
+        <v>120</v>
+      </c>
+      <c r="P59" s="191"/>
       <c r="Q59" s="183"/>
       <c r="R59" s="88"/>
       <c r="S59" s="88"/>
@@ -7320,44 +7338,44 @@
       <c r="U59" s="88"/>
     </row>
     <row r="60" spans="1:21" ht="22.5">
-      <c r="A60" s="203"/>
-      <c r="B60" s="204"/>
-      <c r="C60" s="205"/>
-      <c r="D60" s="205"/>
+      <c r="A60" s="191"/>
+      <c r="B60" s="192"/>
+      <c r="C60" s="193"/>
+      <c r="D60" s="193"/>
       <c r="E60" s="181" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F60" s="175" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="G60" s="179" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="H60" s="175" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I60" s="177" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J60" s="175" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="K60" s="175" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="L60" s="173" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="M60" s="173" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N60" s="171" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="O60" s="171" t="s">
-        <v>638</v>
-      </c>
-      <c r="P60" s="203"/>
+        <v>634</v>
+      </c>
+      <c r="P60" s="191"/>
       <c r="Q60" s="183"/>
       <c r="R60" s="88"/>
       <c r="S60" s="88"/>
@@ -7372,46 +7390,46 @@
         <v>76</v>
       </c>
       <c r="C61" s="186" t="s">
+        <v>635</v>
+      </c>
+      <c r="D61" s="186" t="s">
+        <v>636</v>
+      </c>
+      <c r="E61" s="180" t="s">
+        <v>638</v>
+      </c>
+      <c r="F61" s="174" t="s">
         <v>639</v>
       </c>
-      <c r="D61" s="186" t="s">
+      <c r="G61" s="178" t="s">
         <v>640</v>
-      </c>
-      <c r="E61" s="180" t="s">
-        <v>642</v>
-      </c>
-      <c r="F61" s="174" t="s">
-        <v>643</v>
-      </c>
-      <c r="G61" s="178" t="s">
-        <v>644</v>
       </c>
       <c r="H61" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I61" s="176" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="J61" s="174" t="s">
+        <v>641</v>
+      </c>
+      <c r="K61" s="174" t="s">
+        <v>642</v>
+      </c>
+      <c r="L61" s="172" t="s">
+        <v>643</v>
+      </c>
+      <c r="M61" s="172" t="s">
+        <v>644</v>
+      </c>
+      <c r="N61" s="170" t="s">
         <v>645</v>
       </c>
-      <c r="K61" s="174" t="s">
+      <c r="O61" s="170" t="s">
         <v>646</v>
       </c>
-      <c r="L61" s="172" t="s">
-        <v>647</v>
-      </c>
-      <c r="M61" s="172" t="s">
-        <v>648</v>
-      </c>
-      <c r="N61" s="170" t="s">
-        <v>649</v>
-      </c>
-      <c r="O61" s="170" t="s">
-        <v>650</v>
-      </c>
       <c r="P61" s="168" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="Q61" s="183"/>
       <c r="R61" s="88"/>
@@ -7420,53 +7438,53 @@
       <c r="U61" s="88"/>
     </row>
     <row r="62" spans="1:21" ht="22.5">
-      <c r="A62" s="203" t="s">
+      <c r="A62" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="204" t="s">
+      <c r="B62" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="205" t="s">
+      <c r="C62" s="193" t="s">
+        <v>647</v>
+      </c>
+      <c r="D62" s="193" t="s">
+        <v>648</v>
+      </c>
+      <c r="E62" s="181" t="s">
+        <v>649</v>
+      </c>
+      <c r="F62" s="175" t="s">
+        <v>650</v>
+      </c>
+      <c r="G62" s="179" t="s">
         <v>651</v>
       </c>
-      <c r="D62" s="205" t="s">
+      <c r="H62" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I62" s="177" t="s">
         <v>652</v>
       </c>
-      <c r="E62" s="181" t="s">
+      <c r="J62" s="175" t="s">
         <v>653</v>
       </c>
-      <c r="F62" s="175" t="s">
+      <c r="K62" s="175" t="s">
         <v>654</v>
       </c>
-      <c r="G62" s="179" t="s">
+      <c r="L62" s="173" t="s">
         <v>655</v>
       </c>
-      <c r="H62" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I62" s="177" t="s">
+      <c r="M62" s="173" t="s">
         <v>656</v>
       </c>
-      <c r="J62" s="175" t="s">
+      <c r="N62" s="171" t="s">
         <v>657</v>
       </c>
-      <c r="K62" s="175" t="s">
+      <c r="O62" s="171" t="s">
         <v>658</v>
       </c>
-      <c r="L62" s="173" t="s">
-        <v>659</v>
-      </c>
-      <c r="M62" s="173" t="s">
-        <v>660</v>
-      </c>
-      <c r="N62" s="171" t="s">
-        <v>661</v>
-      </c>
-      <c r="O62" s="171" t="s">
-        <v>662</v>
-      </c>
-      <c r="P62" s="203" t="s">
-        <v>287</v>
+      <c r="P62" s="191" t="s">
+        <v>283</v>
       </c>
       <c r="Q62" s="183"/>
       <c r="R62" s="88"/>
@@ -7475,44 +7493,44 @@
       <c r="U62" s="88"/>
     </row>
     <row r="63" spans="1:21" ht="22.5">
-      <c r="A63" s="203"/>
-      <c r="B63" s="204"/>
-      <c r="C63" s="205"/>
-      <c r="D63" s="205"/>
+      <c r="A63" s="191"/>
+      <c r="B63" s="192"/>
+      <c r="C63" s="193"/>
+      <c r="D63" s="193"/>
       <c r="E63" s="181" t="s">
+        <v>659</v>
+      </c>
+      <c r="F63" s="175" t="s">
+        <v>660</v>
+      </c>
+      <c r="G63" s="179" t="s">
+        <v>661</v>
+      </c>
+      <c r="H63" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="I63" s="177" t="s">
+        <v>662</v>
+      </c>
+      <c r="J63" s="175" t="s">
         <v>663</v>
       </c>
-      <c r="F63" s="175" t="s">
+      <c r="K63" s="175" t="s">
         <v>664</v>
       </c>
-      <c r="G63" s="179" t="s">
+      <c r="L63" s="173" t="s">
         <v>665</v>
       </c>
-      <c r="H63" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="I63" s="177" t="s">
+      <c r="M63" s="173" t="s">
         <v>666</v>
       </c>
-      <c r="J63" s="175" t="s">
+      <c r="N63" s="171" t="s">
         <v>667</v>
       </c>
-      <c r="K63" s="175" t="s">
+      <c r="O63" s="171" t="s">
         <v>668</v>
       </c>
-      <c r="L63" s="173" t="s">
-        <v>669</v>
-      </c>
-      <c r="M63" s="173" t="s">
-        <v>670</v>
-      </c>
-      <c r="N63" s="171" t="s">
-        <v>671</v>
-      </c>
-      <c r="O63" s="171" t="s">
-        <v>672</v>
-      </c>
-      <c r="P63" s="203"/>
+      <c r="P63" s="191"/>
       <c r="Q63" s="183"/>
       <c r="R63" s="88"/>
       <c r="S63" s="88"/>
@@ -7520,53 +7538,53 @@
       <c r="U63" s="88"/>
     </row>
     <row r="64" spans="1:21" ht="22.5">
-      <c r="A64" s="206" t="s">
+      <c r="A64" s="194" t="s">
+        <v>669</v>
+      </c>
+      <c r="B64" s="195" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" s="196" t="s">
+        <v>670</v>
+      </c>
+      <c r="D64" s="196" t="s">
+        <v>671</v>
+      </c>
+      <c r="E64" s="180" t="s">
         <v>673</v>
       </c>
-      <c r="B64" s="207" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="208" t="s">
+      <c r="F64" s="174" t="s">
         <v>674</v>
       </c>
-      <c r="D64" s="208" t="s">
+      <c r="G64" s="178" t="s">
         <v>675</v>
-      </c>
-      <c r="E64" s="180" t="s">
-        <v>677</v>
-      </c>
-      <c r="F64" s="174" t="s">
-        <v>678</v>
-      </c>
-      <c r="G64" s="178" t="s">
-        <v>679</v>
       </c>
       <c r="H64" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I64" s="176" t="s">
+        <v>676</v>
+      </c>
+      <c r="J64" s="174" t="s">
+        <v>677</v>
+      </c>
+      <c r="K64" s="174" t="s">
+        <v>156</v>
+      </c>
+      <c r="L64" s="172" t="s">
+        <v>678</v>
+      </c>
+      <c r="M64" s="172" t="s">
+        <v>270</v>
+      </c>
+      <c r="N64" s="170" t="s">
+        <v>679</v>
+      </c>
+      <c r="O64" s="170" t="s">
         <v>680</v>
       </c>
-      <c r="J64" s="174" t="s">
-        <v>681</v>
-      </c>
-      <c r="K64" s="174" t="s">
-        <v>160</v>
-      </c>
-      <c r="L64" s="172" t="s">
-        <v>682</v>
-      </c>
-      <c r="M64" s="172" t="s">
-        <v>274</v>
-      </c>
-      <c r="N64" s="170" t="s">
-        <v>683</v>
-      </c>
-      <c r="O64" s="170" t="s">
-        <v>684</v>
-      </c>
-      <c r="P64" s="206" t="s">
-        <v>676</v>
+      <c r="P64" s="194" t="s">
+        <v>672</v>
       </c>
       <c r="Q64" s="183"/>
       <c r="R64" s="88"/>
@@ -7575,44 +7593,44 @@
       <c r="U64" s="88"/>
     </row>
     <row r="65" spans="1:21" ht="22.5">
-      <c r="A65" s="206"/>
-      <c r="B65" s="207"/>
-      <c r="C65" s="208"/>
-      <c r="D65" s="208"/>
+      <c r="A65" s="194"/>
+      <c r="B65" s="195"/>
+      <c r="C65" s="196"/>
+      <c r="D65" s="196"/>
       <c r="E65" s="167" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="F65" s="174" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="G65" s="178" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="H65" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I65" s="176" t="s">
+        <v>684</v>
+      </c>
+      <c r="J65" s="174" t="s">
+        <v>685</v>
+      </c>
+      <c r="K65" s="174" t="s">
+        <v>686</v>
+      </c>
+      <c r="L65" s="172" t="s">
+        <v>656</v>
+      </c>
+      <c r="M65" s="172" t="s">
+        <v>687</v>
+      </c>
+      <c r="N65" s="170" t="s">
         <v>688</v>
       </c>
-      <c r="J65" s="174" t="s">
+      <c r="O65" s="170" t="s">
         <v>689</v>
       </c>
-      <c r="K65" s="174" t="s">
-        <v>690</v>
-      </c>
-      <c r="L65" s="172" t="s">
-        <v>660</v>
-      </c>
-      <c r="M65" s="172" t="s">
-        <v>691</v>
-      </c>
-      <c r="N65" s="170" t="s">
-        <v>692</v>
-      </c>
-      <c r="O65" s="170" t="s">
-        <v>693</v>
-      </c>
-      <c r="P65" s="206"/>
+      <c r="P65" s="194"/>
       <c r="Q65" s="183"/>
       <c r="R65" s="88"/>
       <c r="S65" s="88"/>
@@ -7620,44 +7638,44 @@
       <c r="U65" s="88"/>
     </row>
     <row r="66" spans="1:21" ht="22.5">
-      <c r="A66" s="206"/>
-      <c r="B66" s="207"/>
-      <c r="C66" s="208"/>
-      <c r="D66" s="208"/>
+      <c r="A66" s="194"/>
+      <c r="B66" s="195"/>
+      <c r="C66" s="196"/>
+      <c r="D66" s="196"/>
       <c r="E66" s="180" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="F66" s="174" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="G66" s="178" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="H66" s="174" t="s">
         <v>83</v>
       </c>
       <c r="I66" s="176" t="s">
+        <v>693</v>
+      </c>
+      <c r="J66" s="174" t="s">
+        <v>694</v>
+      </c>
+      <c r="K66" s="174" t="s">
+        <v>695</v>
+      </c>
+      <c r="L66" s="172" t="s">
+        <v>696</v>
+      </c>
+      <c r="M66" s="172" t="s">
         <v>697</v>
       </c>
-      <c r="J66" s="174" t="s">
+      <c r="N66" s="170" t="s">
         <v>698</v>
       </c>
-      <c r="K66" s="174" t="s">
+      <c r="O66" s="170" t="s">
         <v>699</v>
       </c>
-      <c r="L66" s="172" t="s">
-        <v>700</v>
-      </c>
-      <c r="M66" s="172" t="s">
-        <v>701</v>
-      </c>
-      <c r="N66" s="170" t="s">
-        <v>702</v>
-      </c>
-      <c r="O66" s="170" t="s">
-        <v>703</v>
-      </c>
-      <c r="P66" s="206"/>
+      <c r="P66" s="194"/>
       <c r="Q66" s="183"/>
       <c r="R66" s="88"/>
       <c r="S66" s="88"/>
@@ -11620,106 +11638,6 @@
     </row>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="P62:P63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="P64:P66"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="P52:P53"/>
-    <mergeCell ref="A54:A60"/>
-    <mergeCell ref="B54:B60"/>
-    <mergeCell ref="C54:C60"/>
-    <mergeCell ref="D54:D60"/>
-    <mergeCell ref="P54:P60"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="P49:P50"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="P41:P43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="P44:P46"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="P32:P34"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="D35:D39"/>
-    <mergeCell ref="P35:P39"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="P28:P31"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="P24:P25"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="P10:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="P8:P9"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
@@ -11734,6 +11652,106 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="P2:P3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="P28:P31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="P32:P34"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="D35:D39"/>
+    <mergeCell ref="P35:P39"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="P41:P43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="P44:P46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="P52:P53"/>
+    <mergeCell ref="A54:A60"/>
+    <mergeCell ref="B54:B60"/>
+    <mergeCell ref="C54:C60"/>
+    <mergeCell ref="D54:D60"/>
+    <mergeCell ref="P54:P60"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="P62:P63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="P64:P66"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <dataValidations count="1">
@@ -11772,26 +11790,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="14.25">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="200" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="193"/>
+      <c r="B1" s="201"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
+      <c r="E1" s="201"/>
+      <c r="F1" s="201"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="201"/>
+      <c r="I1" s="201"/>
+      <c r="J1" s="201"/>
+      <c r="K1" s="201"/>
+      <c r="L1" s="201"/>
+      <c r="M1" s="201"/>
+      <c r="N1" s="201"/>
+      <c r="O1" s="201"/>
+      <c r="P1" s="201"/>
+      <c r="Q1" s="201"/>
+      <c r="R1" s="202"/>
       <c r="S1" s="88"/>
       <c r="T1" s="88"/>
       <c r="U1" s="88"/>
@@ -11799,52 +11817,52 @@
       <c r="W1" s="88"/>
     </row>
     <row r="2" spans="1:23" ht="14.25">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="204" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="197" t="s">
+      <c r="B2" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="198" t="s">
+      <c r="E2" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="195" t="s">
+      <c r="F2" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="197" t="s">
+      <c r="G2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="197" t="s">
+      <c r="H2" s="206" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="197" t="s">
+      <c r="I2" s="206" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="197" t="s">
+      <c r="J2" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="197" t="s">
+      <c r="K2" s="206" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="194" t="s">
+      <c r="L2" s="203" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="193"/>
-      <c r="N2" s="194" t="s">
+      <c r="M2" s="202"/>
+      <c r="N2" s="203" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="193"/>
-      <c r="P2" s="194" t="s">
+      <c r="O2" s="202"/>
+      <c r="P2" s="203" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="193"/>
-      <c r="R2" s="197" t="s">
+      <c r="Q2" s="202"/>
+      <c r="R2" s="206" t="s">
         <v>13</v>
       </c>
       <c r="S2" s="88"/>
@@ -11854,17 +11872,17 @@
       <c r="W2" s="88"/>
     </row>
     <row r="3" spans="1:23" ht="14.25">
-      <c r="A3" s="209"/>
-      <c r="B3" s="209"/>
-      <c r="C3" s="209"/>
-      <c r="D3" s="209"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="209"/>
-      <c r="G3" s="209"/>
-      <c r="H3" s="255"/>
-      <c r="I3" s="255"/>
-      <c r="J3" s="255"/>
-      <c r="K3" s="255"/>
+      <c r="A3" s="228"/>
+      <c r="B3" s="228"/>
+      <c r="C3" s="228"/>
+      <c r="D3" s="228"/>
+      <c r="E3" s="227"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="228"/>
+      <c r="H3" s="229"/>
+      <c r="I3" s="229"/>
+      <c r="J3" s="229"/>
+      <c r="K3" s="229"/>
       <c r="L3" s="90" t="s">
         <v>14</v>
       </c>
@@ -11883,7 +11901,7 @@
       <c r="Q3" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="209"/>
+      <c r="R3" s="228"/>
       <c r="S3" s="88"/>
       <c r="T3" s="88"/>
       <c r="U3" s="88"/>
@@ -11891,12 +11909,12 @@
       <c r="W3" s="88"/>
     </row>
     <row r="4" spans="1:23" ht="14.25">
-      <c r="A4" s="210" t="s">
+      <c r="A4" s="216" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="220"/>
-      <c r="C4" s="229"/>
-      <c r="D4" s="232"/>
+      <c r="B4" s="251"/>
+      <c r="C4" s="239"/>
+      <c r="D4" s="231"/>
       <c r="E4" s="3"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5"/>
@@ -11910,7 +11928,7 @@
       <c r="O4" s="94"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="210" t="s">
+      <c r="R4" s="216" t="s">
         <v>19</v>
       </c>
       <c r="S4" s="88"/>
@@ -11920,10 +11938,10 @@
       <c r="W4" s="88"/>
     </row>
     <row r="5" spans="1:23" ht="14.25">
-      <c r="A5" s="211"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="211"/>
-      <c r="D5" s="211"/>
+      <c r="A5" s="210"/>
+      <c r="B5" s="210"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
       <c r="G5" s="9"/>
@@ -11937,7 +11955,7 @@
       <c r="O5" s="97"/>
       <c r="P5" s="96"/>
       <c r="Q5" s="96"/>
-      <c r="R5" s="211"/>
+      <c r="R5" s="210"/>
       <c r="S5" s="88"/>
       <c r="T5" s="88"/>
       <c r="U5" s="88"/>
@@ -11945,12 +11963,12 @@
       <c r="W5" s="88"/>
     </row>
     <row r="6" spans="1:23" ht="14.25">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="211" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="221"/>
-      <c r="C6" s="230"/>
-      <c r="D6" s="234"/>
+      <c r="B6" s="260"/>
+      <c r="C6" s="253"/>
+      <c r="D6" s="230"/>
       <c r="E6" s="12"/>
       <c r="F6" s="13"/>
       <c r="G6" s="14"/>
@@ -11964,7 +11982,7 @@
       <c r="O6" s="99"/>
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
-      <c r="R6" s="212" t="s">
+      <c r="R6" s="211" t="s">
         <v>21</v>
       </c>
       <c r="S6" s="88"/>
@@ -11974,10 +11992,10 @@
       <c r="W6" s="88"/>
     </row>
     <row r="7" spans="1:23" ht="14.25">
-      <c r="A7" s="211"/>
-      <c r="B7" s="219"/>
-      <c r="C7" s="231"/>
-      <c r="D7" s="211"/>
+      <c r="A7" s="210"/>
+      <c r="B7" s="259"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="210"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
@@ -11991,7 +12009,7 @@
       <c r="O7" s="100"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
-      <c r="R7" s="211"/>
+      <c r="R7" s="210"/>
       <c r="S7" s="88"/>
       <c r="T7" s="88"/>
       <c r="U7" s="88"/>
@@ -11999,12 +12017,12 @@
       <c r="W7" s="88"/>
     </row>
     <row r="8" spans="1:23" ht="14.25">
-      <c r="A8" s="210" t="s">
+      <c r="A8" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="220"/>
-      <c r="C8" s="232"/>
-      <c r="D8" s="232"/>
+      <c r="B8" s="251"/>
+      <c r="C8" s="231"/>
+      <c r="D8" s="231"/>
       <c r="E8" s="20"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2"/>
@@ -12018,7 +12036,7 @@
       <c r="O8" s="102"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="210" t="s">
+      <c r="R8" s="216" t="s">
         <v>23</v>
       </c>
       <c r="S8" s="88"/>
@@ -12028,10 +12046,10 @@
       <c r="W8" s="88"/>
     </row>
     <row r="9" spans="1:23" ht="14.25">
-      <c r="A9" s="211"/>
-      <c r="B9" s="211"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="211"/>
+      <c r="A9" s="210"/>
+      <c r="B9" s="210"/>
+      <c r="C9" s="221"/>
+      <c r="D9" s="210"/>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
       <c r="G9" s="22"/>
@@ -12045,7 +12063,7 @@
       <c r="O9" s="103"/>
       <c r="P9" s="21"/>
       <c r="Q9" s="21"/>
-      <c r="R9" s="211"/>
+      <c r="R9" s="210"/>
       <c r="S9" s="88"/>
       <c r="T9" s="88"/>
       <c r="U9" s="88"/>
@@ -12053,12 +12071,12 @@
       <c r="W9" s="88"/>
     </row>
     <row r="10" spans="1:23" ht="14.25">
-      <c r="A10" s="212" t="s">
+      <c r="A10" s="211" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="221"/>
-      <c r="C10" s="234"/>
-      <c r="D10" s="246"/>
+      <c r="B10" s="260"/>
+      <c r="C10" s="230"/>
+      <c r="D10" s="237"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="24"/>
@@ -12072,7 +12090,7 @@
       <c r="O10" s="105"/>
       <c r="P10" s="37"/>
       <c r="Q10" s="37"/>
-      <c r="R10" s="212" t="s">
+      <c r="R10" s="211" t="s">
         <v>23</v>
       </c>
       <c r="S10" s="88"/>
@@ -12082,10 +12100,10 @@
       <c r="W10" s="88"/>
     </row>
     <row r="11" spans="1:23" ht="14.25">
-      <c r="A11" s="211"/>
-      <c r="B11" s="219"/>
-      <c r="C11" s="211"/>
-      <c r="D11" s="233"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="259"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="221"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
       <c r="G11" s="24"/>
@@ -12099,7 +12117,7 @@
       <c r="O11" s="106"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
-      <c r="R11" s="211"/>
+      <c r="R11" s="210"/>
       <c r="S11" s="88"/>
       <c r="T11" s="88"/>
       <c r="U11" s="88"/>
@@ -12107,12 +12125,12 @@
       <c r="W11" s="88"/>
     </row>
     <row r="12" spans="1:23" ht="14.25">
-      <c r="A12" s="210" t="s">
+      <c r="A12" s="216" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="220"/>
-      <c r="C12" s="232"/>
-      <c r="D12" s="232"/>
+      <c r="B12" s="251"/>
+      <c r="C12" s="231"/>
+      <c r="D12" s="231"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
       <c r="G12" s="5"/>
@@ -12126,7 +12144,7 @@
       <c r="O12" s="109"/>
       <c r="P12" s="110"/>
       <c r="Q12" s="110"/>
-      <c r="R12" s="210" t="s">
+      <c r="R12" s="216" t="s">
         <v>19</v>
       </c>
       <c r="S12" s="88"/>
@@ -12136,10 +12154,10 @@
       <c r="W12" s="88"/>
     </row>
     <row r="13" spans="1:23" ht="14.25">
-      <c r="A13" s="211"/>
-      <c r="B13" s="211"/>
-      <c r="C13" s="211"/>
-      <c r="D13" s="211"/>
+      <c r="A13" s="210"/>
+      <c r="B13" s="210"/>
+      <c r="C13" s="210"/>
+      <c r="D13" s="210"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="27"/>
@@ -12153,7 +12171,7 @@
       <c r="O13" s="112"/>
       <c r="P13" s="110"/>
       <c r="Q13" s="110"/>
-      <c r="R13" s="211"/>
+      <c r="R13" s="210"/>
       <c r="S13" s="88"/>
       <c r="T13" s="88"/>
       <c r="U13" s="88"/>
@@ -12161,12 +12179,12 @@
       <c r="W13" s="88"/>
     </row>
     <row r="14" spans="1:23" ht="14.25">
-      <c r="A14" s="212" t="s">
+      <c r="A14" s="211" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="222"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="234"/>
+      <c r="B14" s="250"/>
+      <c r="C14" s="230"/>
+      <c r="D14" s="230"/>
       <c r="E14" s="12"/>
       <c r="F14" s="13"/>
       <c r="G14" s="11"/>
@@ -12180,7 +12198,7 @@
       <c r="O14" s="99"/>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
-      <c r="R14" s="212" t="s">
+      <c r="R14" s="211" t="s">
         <v>27</v>
       </c>
       <c r="S14" s="88"/>
@@ -12190,10 +12208,10 @@
       <c r="W14" s="88"/>
     </row>
     <row r="15" spans="1:23" ht="14.25">
-      <c r="A15" s="211"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="211"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="210"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31"/>
       <c r="G15" s="32"/>
@@ -12207,7 +12225,7 @@
       <c r="O15" s="115"/>
       <c r="P15" s="31"/>
       <c r="Q15" s="31"/>
-      <c r="R15" s="211"/>
+      <c r="R15" s="210"/>
       <c r="S15" s="88"/>
       <c r="T15" s="88"/>
       <c r="U15" s="88"/>
@@ -12215,12 +12233,12 @@
       <c r="W15" s="88"/>
     </row>
     <row r="16" spans="1:23" ht="14.25">
-      <c r="A16" s="210" t="s">
+      <c r="A16" s="216" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="220"/>
-      <c r="C16" s="229"/>
-      <c r="D16" s="232"/>
+      <c r="B16" s="251"/>
+      <c r="C16" s="239"/>
+      <c r="D16" s="231"/>
       <c r="E16" s="33"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2"/>
@@ -12234,7 +12252,7 @@
       <c r="O16" s="92"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="210" t="s">
+      <c r="R16" s="216" t="s">
         <v>29</v>
       </c>
       <c r="S16" s="88"/>
@@ -12244,10 +12262,10 @@
       <c r="W16" s="88"/>
     </row>
     <row r="17" spans="1:23" ht="14.25">
-      <c r="A17" s="211"/>
-      <c r="B17" s="211"/>
-      <c r="C17" s="211"/>
-      <c r="D17" s="211"/>
+      <c r="A17" s="210"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="210"/>
+      <c r="D17" s="210"/>
       <c r="E17" s="33"/>
       <c r="F17" s="33"/>
       <c r="G17" s="34"/>
@@ -12261,7 +12279,7 @@
       <c r="O17" s="101"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="211"/>
+      <c r="R17" s="210"/>
       <c r="S17" s="88"/>
       <c r="T17" s="88"/>
       <c r="U17" s="88"/>
@@ -12269,12 +12287,12 @@
       <c r="W17" s="88"/>
     </row>
     <row r="18" spans="1:23" ht="14.25">
-      <c r="A18" s="212" t="s">
+      <c r="A18" s="211" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="222"/>
-      <c r="C18" s="235"/>
-      <c r="D18" s="247"/>
+      <c r="B18" s="250"/>
+      <c r="C18" s="255"/>
+      <c r="D18" s="238"/>
       <c r="E18" s="37"/>
       <c r="F18" s="37"/>
       <c r="G18" s="35"/>
@@ -12288,7 +12306,7 @@
       <c r="O18" s="117"/>
       <c r="P18" s="38"/>
       <c r="Q18" s="38"/>
-      <c r="R18" s="212" t="s">
+      <c r="R18" s="211" t="s">
         <v>31</v>
       </c>
       <c r="S18" s="162"/>
@@ -12298,10 +12316,10 @@
       <c r="W18" s="162"/>
     </row>
     <row r="19" spans="1:23" ht="14.25">
-      <c r="A19" s="211"/>
-      <c r="B19" s="211"/>
-      <c r="C19" s="211"/>
-      <c r="D19" s="211"/>
+      <c r="A19" s="210"/>
+      <c r="B19" s="210"/>
+      <c r="C19" s="210"/>
+      <c r="D19" s="210"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
       <c r="G19" s="24"/>
@@ -12315,7 +12333,7 @@
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
-      <c r="R19" s="211"/>
+      <c r="R19" s="210"/>
       <c r="S19" s="88"/>
       <c r="T19" s="88"/>
       <c r="U19" s="88"/>
@@ -12323,12 +12341,12 @@
       <c r="W19" s="88"/>
     </row>
     <row r="20" spans="1:23" ht="14.25">
-      <c r="A20" s="210" t="s">
+      <c r="A20" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="220"/>
-      <c r="C20" s="232"/>
-      <c r="D20" s="232"/>
+      <c r="B20" s="251"/>
+      <c r="C20" s="231"/>
+      <c r="D20" s="231"/>
       <c r="E20" s="39"/>
       <c r="F20" s="25"/>
       <c r="G20" s="40"/>
@@ -12342,7 +12360,7 @@
       <c r="O20" s="119"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
-      <c r="R20" s="210" t="s">
+      <c r="R20" s="216" t="s">
         <v>33</v>
       </c>
       <c r="S20" s="88"/>
@@ -12352,10 +12370,10 @@
       <c r="W20" s="88"/>
     </row>
     <row r="21" spans="1:23" ht="14.25">
-      <c r="A21" s="211"/>
-      <c r="B21" s="211"/>
-      <c r="C21" s="211"/>
-      <c r="D21" s="211"/>
+      <c r="A21" s="210"/>
+      <c r="B21" s="210"/>
+      <c r="C21" s="210"/>
+      <c r="D21" s="210"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="27"/>
@@ -12369,7 +12387,7 @@
       <c r="O21" s="120"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
-      <c r="R21" s="211"/>
+      <c r="R21" s="210"/>
       <c r="S21" s="88"/>
       <c r="T21" s="88"/>
       <c r="U21" s="88"/>
@@ -12377,12 +12395,12 @@
       <c r="W21" s="88"/>
     </row>
     <row r="22" spans="1:23" ht="14.25">
-      <c r="A22" s="212" t="s">
+      <c r="A22" s="211" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="222"/>
-      <c r="C22" s="236"/>
-      <c r="D22" s="236"/>
+      <c r="B22" s="250"/>
+      <c r="C22" s="226"/>
+      <c r="D22" s="226"/>
       <c r="E22" s="42"/>
       <c r="F22" s="42"/>
       <c r="G22" s="41"/>
@@ -12396,7 +12414,7 @@
       <c r="O22" s="117"/>
       <c r="P22" s="121"/>
       <c r="Q22" s="121"/>
-      <c r="R22" s="212" t="s">
+      <c r="R22" s="211" t="s">
         <v>35</v>
       </c>
       <c r="S22" s="88"/>
@@ -12406,10 +12424,10 @@
       <c r="W22" s="88"/>
     </row>
     <row r="23" spans="1:23" ht="14.25">
-      <c r="A23" s="211"/>
-      <c r="B23" s="211"/>
-      <c r="C23" s="211"/>
-      <c r="D23" s="211"/>
+      <c r="A23" s="210"/>
+      <c r="B23" s="210"/>
+      <c r="C23" s="210"/>
+      <c r="D23" s="210"/>
       <c r="E23" s="42"/>
       <c r="F23" s="15"/>
       <c r="G23" s="24"/>
@@ -12423,7 +12441,7 @@
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
-      <c r="R23" s="211"/>
+      <c r="R23" s="210"/>
       <c r="S23" s="88"/>
       <c r="T23" s="88"/>
       <c r="U23" s="88"/>
@@ -12431,12 +12449,12 @@
       <c r="W23" s="88"/>
     </row>
     <row r="24" spans="1:23" ht="14.25">
-      <c r="A24" s="210" t="s">
+      <c r="A24" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="220"/>
-      <c r="C24" s="237"/>
-      <c r="D24" s="229"/>
+      <c r="B24" s="251"/>
+      <c r="C24" s="242"/>
+      <c r="D24" s="239"/>
       <c r="E24" s="21"/>
       <c r="F24" s="3"/>
       <c r="G24" s="34"/>
@@ -12450,7 +12468,7 @@
       <c r="O24" s="92"/>
       <c r="P24" s="116"/>
       <c r="Q24" s="103"/>
-      <c r="R24" s="210" t="s">
+      <c r="R24" s="216" t="s">
         <v>37</v>
       </c>
       <c r="S24" s="88"/>
@@ -12460,10 +12478,10 @@
       <c r="W24" s="88"/>
     </row>
     <row r="25" spans="1:23" ht="14.25">
-      <c r="A25" s="211"/>
-      <c r="B25" s="211"/>
-      <c r="C25" s="231"/>
-      <c r="D25" s="211"/>
+      <c r="A25" s="210"/>
+      <c r="B25" s="210"/>
+      <c r="C25" s="254"/>
+      <c r="D25" s="210"/>
       <c r="E25" s="21"/>
       <c r="F25" s="3"/>
       <c r="G25" s="22"/>
@@ -12477,7 +12495,7 @@
       <c r="O25" s="122"/>
       <c r="P25" s="33"/>
       <c r="Q25" s="21"/>
-      <c r="R25" s="211"/>
+      <c r="R25" s="210"/>
       <c r="S25" s="88"/>
       <c r="T25" s="88"/>
       <c r="U25" s="88"/>
@@ -12485,12 +12503,12 @@
       <c r="W25" s="88"/>
     </row>
     <row r="26" spans="1:23" ht="14.25">
-      <c r="A26" s="213" t="s">
+      <c r="A26" s="222" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="223"/>
-      <c r="C26" s="238"/>
-      <c r="D26" s="238"/>
+      <c r="B26" s="261"/>
+      <c r="C26" s="240"/>
+      <c r="D26" s="240"/>
       <c r="E26" s="42"/>
       <c r="F26" s="42"/>
       <c r="G26" s="41"/>
@@ -12504,7 +12522,7 @@
       <c r="O26" s="113"/>
       <c r="P26" s="42"/>
       <c r="Q26" s="42"/>
-      <c r="R26" s="213" t="s">
+      <c r="R26" s="222" t="s">
         <v>39</v>
       </c>
       <c r="S26" s="88"/>
@@ -12514,10 +12532,10 @@
       <c r="W26" s="88"/>
     </row>
     <row r="27" spans="1:23" ht="14.25">
-      <c r="A27" s="214"/>
-      <c r="B27" s="214"/>
-      <c r="C27" s="214"/>
-      <c r="D27" s="248"/>
+      <c r="A27" s="220"/>
+      <c r="B27" s="220"/>
+      <c r="C27" s="220"/>
+      <c r="D27" s="241"/>
       <c r="E27" s="43"/>
       <c r="F27" s="44"/>
       <c r="G27" s="45"/>
@@ -12531,7 +12549,7 @@
       <c r="O27" s="124"/>
       <c r="P27" s="43"/>
       <c r="Q27" s="43"/>
-      <c r="R27" s="256"/>
+      <c r="R27" s="223"/>
       <c r="S27" s="88"/>
       <c r="T27" s="88"/>
       <c r="U27" s="88"/>
@@ -12539,12 +12557,12 @@
       <c r="W27" s="88"/>
     </row>
     <row r="28" spans="1:23" ht="14.25">
-      <c r="A28" s="210" t="s">
+      <c r="A28" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="224"/>
-      <c r="C28" s="237"/>
-      <c r="D28" s="237"/>
+      <c r="B28" s="262"/>
+      <c r="C28" s="242"/>
+      <c r="D28" s="242"/>
       <c r="E28" s="46"/>
       <c r="F28" s="26"/>
       <c r="G28" s="47"/>
@@ -12558,7 +12576,7 @@
       <c r="O28" s="92"/>
       <c r="P28" s="103"/>
       <c r="Q28" s="103"/>
-      <c r="R28" s="257" t="s">
+      <c r="R28" s="224" t="s">
         <v>41</v>
       </c>
       <c r="S28" s="88"/>
@@ -12568,10 +12586,10 @@
       <c r="W28" s="88"/>
     </row>
     <row r="29" spans="1:23" ht="14.25">
-      <c r="A29" s="211"/>
-      <c r="B29" s="211"/>
-      <c r="C29" s="231"/>
-      <c r="D29" s="233"/>
+      <c r="A29" s="210"/>
+      <c r="B29" s="210"/>
+      <c r="C29" s="254"/>
+      <c r="D29" s="221"/>
       <c r="E29" s="48"/>
       <c r="F29" s="48"/>
       <c r="G29" s="49"/>
@@ -12585,7 +12603,7 @@
       <c r="O29" s="48"/>
       <c r="P29" s="33"/>
       <c r="Q29" s="21"/>
-      <c r="R29" s="193"/>
+      <c r="R29" s="202"/>
       <c r="S29" s="88"/>
       <c r="T29" s="88"/>
       <c r="U29" s="88"/>
@@ -12593,12 +12611,12 @@
       <c r="W29" s="88"/>
     </row>
     <row r="30" spans="1:23" ht="14.25">
-      <c r="A30" s="212" t="s">
+      <c r="A30" s="211" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="222"/>
-      <c r="C30" s="236"/>
-      <c r="D30" s="249"/>
+      <c r="B30" s="250"/>
+      <c r="C30" s="226"/>
+      <c r="D30" s="243"/>
       <c r="E30" s="42"/>
       <c r="F30" s="42"/>
       <c r="G30" s="41"/>
@@ -12612,7 +12630,7 @@
       <c r="O30" s="129"/>
       <c r="P30" s="130"/>
       <c r="Q30" s="130"/>
-      <c r="R30" s="258" t="s">
+      <c r="R30" s="215" t="s">
         <v>43</v>
       </c>
       <c r="S30" s="88"/>
@@ -12622,10 +12640,10 @@
       <c r="W30" s="88"/>
     </row>
     <row r="31" spans="1:23" ht="14.25">
-      <c r="A31" s="211"/>
-      <c r="B31" s="211"/>
-      <c r="C31" s="211"/>
-      <c r="D31" s="211"/>
+      <c r="A31" s="210"/>
+      <c r="B31" s="210"/>
+      <c r="C31" s="210"/>
+      <c r="D31" s="210"/>
       <c r="E31" s="50"/>
       <c r="F31" s="50"/>
       <c r="G31" s="51"/>
@@ -12639,7 +12657,7 @@
       <c r="O31" s="114"/>
       <c r="P31" s="50"/>
       <c r="Q31" s="50"/>
-      <c r="R31" s="211"/>
+      <c r="R31" s="210"/>
       <c r="S31" s="88"/>
       <c r="T31" s="88"/>
       <c r="U31" s="88"/>
@@ -12647,12 +12665,12 @@
       <c r="W31" s="88"/>
     </row>
     <row r="32" spans="1:23" ht="14.25">
-      <c r="A32" s="210" t="s">
+      <c r="A32" s="216" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="220"/>
-      <c r="C32" s="232"/>
-      <c r="D32" s="232"/>
+      <c r="B32" s="251"/>
+      <c r="C32" s="231"/>
+      <c r="D32" s="231"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="2"/>
@@ -12666,7 +12684,7 @@
       <c r="O32" s="92"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
-      <c r="R32" s="210" t="s">
+      <c r="R32" s="216" t="s">
         <v>43</v>
       </c>
       <c r="S32" s="88"/>
@@ -12676,10 +12694,10 @@
       <c r="W32" s="88"/>
     </row>
     <row r="33" spans="1:23" ht="14.25">
-      <c r="A33" s="211"/>
-      <c r="B33" s="211"/>
-      <c r="C33" s="211"/>
-      <c r="D33" s="211"/>
+      <c r="A33" s="210"/>
+      <c r="B33" s="210"/>
+      <c r="C33" s="210"/>
+      <c r="D33" s="210"/>
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
       <c r="G33" s="34"/>
@@ -12693,7 +12711,7 @@
       <c r="O33" s="101"/>
       <c r="P33" s="33"/>
       <c r="Q33" s="33"/>
-      <c r="R33" s="211"/>
+      <c r="R33" s="210"/>
       <c r="S33" s="88"/>
       <c r="T33" s="88"/>
       <c r="U33" s="88"/>
@@ -12701,12 +12719,12 @@
       <c r="W33" s="88"/>
     </row>
     <row r="34" spans="1:23" ht="14.25">
-      <c r="A34" s="212" t="s">
+      <c r="A34" s="211" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="222"/>
-      <c r="C34" s="239"/>
-      <c r="D34" s="239"/>
+      <c r="B34" s="250"/>
+      <c r="C34" s="244"/>
+      <c r="D34" s="244"/>
       <c r="E34" s="52"/>
       <c r="F34" s="42"/>
       <c r="G34" s="41"/>
@@ -12720,7 +12738,7 @@
       <c r="O34" s="42"/>
       <c r="P34" s="130"/>
       <c r="Q34" s="130"/>
-      <c r="R34" s="259" t="s">
+      <c r="R34" s="217" t="s">
         <v>46</v>
       </c>
       <c r="S34" s="88"/>
@@ -12730,10 +12748,10 @@
       <c r="W34" s="88"/>
     </row>
     <row r="35" spans="1:23" ht="14.25">
-      <c r="A35" s="212"/>
-      <c r="B35" s="222"/>
-      <c r="C35" s="211"/>
-      <c r="D35" s="211"/>
+      <c r="A35" s="211"/>
+      <c r="B35" s="250"/>
+      <c r="C35" s="210"/>
+      <c r="D35" s="210"/>
       <c r="E35" s="52"/>
       <c r="F35" s="42"/>
       <c r="G35" s="41"/>
@@ -12747,7 +12765,7 @@
       <c r="O35" s="42"/>
       <c r="P35" s="130"/>
       <c r="Q35" s="130"/>
-      <c r="R35" s="260"/>
+      <c r="R35" s="218"/>
       <c r="S35" s="88"/>
       <c r="T35" s="88"/>
       <c r="U35" s="88"/>
@@ -12755,12 +12773,12 @@
       <c r="W35" s="88"/>
     </row>
     <row r="36" spans="1:23" ht="14.25">
-      <c r="A36" s="210" t="s">
+      <c r="A36" s="216" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="220"/>
-      <c r="C36" s="232"/>
-      <c r="D36" s="232"/>
+      <c r="B36" s="251"/>
+      <c r="C36" s="231"/>
+      <c r="D36" s="231"/>
       <c r="E36" s="53"/>
       <c r="F36" s="54"/>
       <c r="G36" s="5"/>
@@ -12774,7 +12792,7 @@
       <c r="O36" s="94"/>
       <c r="P36" s="131"/>
       <c r="Q36" s="131"/>
-      <c r="R36" s="210" t="s">
+      <c r="R36" s="216" t="s">
         <v>48</v>
       </c>
       <c r="S36" s="88"/>
@@ -12784,10 +12802,10 @@
       <c r="W36" s="88"/>
     </row>
     <row r="37" spans="1:23" ht="14.25">
-      <c r="A37" s="211"/>
-      <c r="B37" s="211"/>
-      <c r="C37" s="211"/>
-      <c r="D37" s="211"/>
+      <c r="A37" s="210"/>
+      <c r="B37" s="210"/>
+      <c r="C37" s="210"/>
+      <c r="D37" s="210"/>
       <c r="E37" s="53"/>
       <c r="F37" s="54"/>
       <c r="G37" s="5"/>
@@ -12801,7 +12819,7 @@
       <c r="O37" s="132"/>
       <c r="P37" s="135"/>
       <c r="Q37" s="135"/>
-      <c r="R37" s="217"/>
+      <c r="R37" s="213"/>
       <c r="S37" s="88"/>
       <c r="T37" s="88"/>
       <c r="U37" s="88"/>
@@ -12809,12 +12827,12 @@
       <c r="W37" s="88"/>
     </row>
     <row r="38" spans="1:23" ht="14.25">
-      <c r="A38" s="212" t="s">
+      <c r="A38" s="211" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="222"/>
-      <c r="C38" s="234"/>
-      <c r="D38" s="234"/>
+      <c r="B38" s="250"/>
+      <c r="C38" s="230"/>
+      <c r="D38" s="230"/>
       <c r="E38" s="12"/>
       <c r="F38" s="13"/>
       <c r="G38" s="11"/>
@@ -12828,7 +12846,7 @@
       <c r="O38" s="99"/>
       <c r="P38" s="136"/>
       <c r="Q38" s="136"/>
-      <c r="R38" s="212" t="s">
+      <c r="R38" s="211" t="s">
         <v>50</v>
       </c>
       <c r="S38" s="88"/>
@@ -12838,10 +12856,10 @@
       <c r="W38" s="88"/>
     </row>
     <row r="39" spans="1:23" ht="14.25">
-      <c r="A39" s="211"/>
-      <c r="B39" s="211"/>
-      <c r="C39" s="211"/>
-      <c r="D39" s="211"/>
+      <c r="A39" s="210"/>
+      <c r="B39" s="210"/>
+      <c r="C39" s="210"/>
+      <c r="D39" s="210"/>
       <c r="E39" s="56"/>
       <c r="F39" s="31"/>
       <c r="G39" s="57"/>
@@ -12855,7 +12873,7 @@
       <c r="O39" s="115"/>
       <c r="P39" s="87"/>
       <c r="Q39" s="87"/>
-      <c r="R39" s="211"/>
+      <c r="R39" s="210"/>
       <c r="S39" s="88"/>
       <c r="T39" s="88"/>
       <c r="U39" s="88"/>
@@ -12863,12 +12881,12 @@
       <c r="W39" s="88"/>
     </row>
     <row r="40" spans="1:23" ht="14.25">
-      <c r="A40" s="215" t="s">
+      <c r="A40" s="219" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="225"/>
-      <c r="C40" s="240"/>
-      <c r="D40" s="250"/>
+      <c r="B40" s="256"/>
+      <c r="C40" s="247"/>
+      <c r="D40" s="245"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="58"/>
@@ -12882,7 +12900,7 @@
       <c r="O40" s="94"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-      <c r="R40" s="215" t="s">
+      <c r="R40" s="219" t="s">
         <v>52</v>
       </c>
       <c r="S40" s="88"/>
@@ -12892,10 +12910,10 @@
       <c r="W40" s="88"/>
     </row>
     <row r="41" spans="1:23" ht="14.25">
-      <c r="A41" s="214"/>
-      <c r="B41" s="214"/>
-      <c r="C41" s="214"/>
-      <c r="D41" s="251"/>
+      <c r="A41" s="220"/>
+      <c r="B41" s="220"/>
+      <c r="C41" s="220"/>
+      <c r="D41" s="246"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="58"/>
@@ -12909,7 +12927,7 @@
       <c r="O41" s="94"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
-      <c r="R41" s="214"/>
+      <c r="R41" s="220"/>
       <c r="S41" s="88"/>
       <c r="T41" s="88"/>
       <c r="U41" s="88"/>
@@ -12917,12 +12935,12 @@
       <c r="W41" s="88"/>
     </row>
     <row r="42" spans="1:23" ht="14.25">
-      <c r="A42" s="212" t="s">
+      <c r="A42" s="211" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="222"/>
-      <c r="C42" s="234"/>
-      <c r="D42" s="234"/>
+      <c r="B42" s="250"/>
+      <c r="C42" s="230"/>
+      <c r="D42" s="230"/>
       <c r="E42" s="59"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
@@ -12936,7 +12954,7 @@
       <c r="O42" s="138"/>
       <c r="P42" s="59"/>
       <c r="Q42" s="59"/>
-      <c r="R42" s="212" t="s">
+      <c r="R42" s="211" t="s">
         <v>54</v>
       </c>
       <c r="S42" s="88"/>
@@ -12946,10 +12964,10 @@
       <c r="W42" s="88"/>
     </row>
     <row r="43" spans="1:23" ht="14.25">
-      <c r="A43" s="211"/>
-      <c r="B43" s="211"/>
-      <c r="C43" s="211"/>
-      <c r="D43" s="211"/>
+      <c r="A43" s="210"/>
+      <c r="B43" s="210"/>
+      <c r="C43" s="210"/>
+      <c r="D43" s="210"/>
       <c r="E43" s="60"/>
       <c r="F43" s="31"/>
       <c r="G43" s="32"/>
@@ -12963,7 +12981,7 @@
       <c r="O43" s="115"/>
       <c r="P43" s="31"/>
       <c r="Q43" s="15"/>
-      <c r="R43" s="233"/>
+      <c r="R43" s="221"/>
       <c r="S43" s="88"/>
       <c r="T43" s="88"/>
       <c r="U43" s="88"/>
@@ -12971,12 +12989,12 @@
       <c r="W43" s="88"/>
     </row>
     <row r="44" spans="1:23" ht="14.25">
-      <c r="A44" s="210" t="s">
+      <c r="A44" s="216" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="220"/>
-      <c r="C44" s="241"/>
-      <c r="D44" s="232"/>
+      <c r="B44" s="251"/>
+      <c r="C44" s="248"/>
+      <c r="D44" s="231"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="58"/>
@@ -12990,7 +13008,7 @@
       <c r="O44" s="137"/>
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
-      <c r="R44" s="210" t="s">
+      <c r="R44" s="216" t="s">
         <v>56</v>
       </c>
       <c r="S44" s="88"/>
@@ -13000,10 +13018,10 @@
       <c r="W44" s="88"/>
     </row>
     <row r="45" spans="1:23" ht="14.25">
-      <c r="A45" s="211"/>
-      <c r="B45" s="211"/>
-      <c r="C45" s="211"/>
-      <c r="D45" s="211"/>
+      <c r="A45" s="210"/>
+      <c r="B45" s="210"/>
+      <c r="C45" s="210"/>
+      <c r="D45" s="210"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="61"/>
@@ -13017,7 +13035,7 @@
       <c r="O45" s="112"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="8"/>
-      <c r="R45" s="211"/>
+      <c r="R45" s="210"/>
       <c r="S45" s="88"/>
       <c r="T45" s="88"/>
       <c r="U45" s="88"/>
@@ -13025,12 +13043,12 @@
       <c r="W45" s="88"/>
     </row>
     <row r="46" spans="1:23" ht="14.25">
-      <c r="A46" s="216" t="s">
+      <c r="A46" s="263" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="226"/>
-      <c r="C46" s="242"/>
-      <c r="D46" s="242"/>
+      <c r="B46" s="257"/>
+      <c r="C46" s="232"/>
+      <c r="D46" s="232"/>
       <c r="E46" s="63"/>
       <c r="F46" s="15"/>
       <c r="G46" s="36"/>
@@ -13044,7 +13062,7 @@
       <c r="O46" s="113"/>
       <c r="P46" s="38"/>
       <c r="Q46" s="38"/>
-      <c r="R46" s="212" t="s">
+      <c r="R46" s="211" t="s">
         <v>58</v>
       </c>
       <c r="S46" s="88"/>
@@ -13054,10 +13072,10 @@
       <c r="W46" s="88"/>
     </row>
     <row r="47" spans="1:23" ht="14.25">
-      <c r="A47" s="216"/>
-      <c r="B47" s="226"/>
-      <c r="C47" s="242"/>
-      <c r="D47" s="242"/>
+      <c r="A47" s="263"/>
+      <c r="B47" s="257"/>
+      <c r="C47" s="232"/>
+      <c r="D47" s="232"/>
       <c r="E47" s="63"/>
       <c r="F47" s="15"/>
       <c r="G47" s="36"/>
@@ -13071,7 +13089,7 @@
       <c r="O47" s="106"/>
       <c r="P47" s="15"/>
       <c r="Q47" s="15"/>
-      <c r="R47" s="212"/>
+      <c r="R47" s="211"/>
       <c r="S47" s="88"/>
       <c r="T47" s="88"/>
       <c r="U47" s="88"/>
@@ -13079,12 +13097,12 @@
       <c r="W47" s="88"/>
     </row>
     <row r="48" spans="1:23" ht="14.25">
-      <c r="A48" s="210" t="s">
+      <c r="A48" s="216" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="220"/>
-      <c r="C48" s="232"/>
-      <c r="D48" s="232"/>
+      <c r="B48" s="251"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
       <c r="E48" s="64"/>
       <c r="F48" s="64"/>
       <c r="G48" s="65"/>
@@ -13098,7 +13116,7 @@
       <c r="O48" s="141"/>
       <c r="P48" s="66"/>
       <c r="Q48" s="66"/>
-      <c r="R48" s="261" t="s">
+      <c r="R48" s="209" t="s">
         <v>60</v>
       </c>
       <c r="S48" s="88"/>
@@ -13108,10 +13126,10 @@
       <c r="W48" s="88"/>
     </row>
     <row r="49" spans="1:23" ht="14.25">
-      <c r="A49" s="211"/>
-      <c r="B49" s="211"/>
-      <c r="C49" s="211"/>
-      <c r="D49" s="211"/>
+      <c r="A49" s="210"/>
+      <c r="B49" s="210"/>
+      <c r="C49" s="210"/>
+      <c r="D49" s="210"/>
       <c r="E49" s="33"/>
       <c r="F49" s="33"/>
       <c r="G49" s="67"/>
@@ -13125,7 +13143,7 @@
       <c r="O49" s="143"/>
       <c r="P49" s="33"/>
       <c r="Q49" s="33"/>
-      <c r="R49" s="211"/>
+      <c r="R49" s="210"/>
       <c r="S49" s="88"/>
       <c r="T49" s="88"/>
       <c r="U49" s="88"/>
@@ -13133,12 +13151,12 @@
       <c r="W49" s="88"/>
     </row>
     <row r="50" spans="1:23" ht="14.25">
-      <c r="A50" s="212" t="s">
+      <c r="A50" s="211" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="222"/>
-      <c r="C50" s="236"/>
-      <c r="D50" s="236"/>
+      <c r="B50" s="250"/>
+      <c r="C50" s="226"/>
+      <c r="D50" s="226"/>
       <c r="E50" s="12"/>
       <c r="F50" s="13"/>
       <c r="G50" s="68"/>
@@ -13152,7 +13170,7 @@
       <c r="O50" s="145"/>
       <c r="P50" s="19"/>
       <c r="Q50" s="19"/>
-      <c r="R50" s="212" t="s">
+      <c r="R50" s="211" t="s">
         <v>62</v>
       </c>
       <c r="S50" s="88"/>
@@ -13162,10 +13180,10 @@
       <c r="W50" s="88"/>
     </row>
     <row r="51" spans="1:23" ht="14.25">
-      <c r="A51" s="211"/>
-      <c r="B51" s="211"/>
-      <c r="C51" s="211"/>
-      <c r="D51" s="211"/>
+      <c r="A51" s="210"/>
+      <c r="B51" s="210"/>
+      <c r="C51" s="210"/>
+      <c r="D51" s="210"/>
       <c r="E51" s="12"/>
       <c r="F51" s="13"/>
       <c r="G51" s="68"/>
@@ -13179,7 +13197,7 @@
       <c r="O51" s="145"/>
       <c r="P51" s="19"/>
       <c r="Q51" s="19"/>
-      <c r="R51" s="211"/>
+      <c r="R51" s="210"/>
       <c r="S51" s="88"/>
       <c r="T51" s="88"/>
       <c r="U51" s="88"/>
@@ -13187,12 +13205,12 @@
       <c r="W51" s="88"/>
     </row>
     <row r="52" spans="1:23" ht="14.25">
-      <c r="A52" s="210" t="s">
+      <c r="A52" s="216" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="227"/>
-      <c r="C52" s="232"/>
-      <c r="D52" s="252"/>
+      <c r="B52" s="249"/>
+      <c r="C52" s="231"/>
+      <c r="D52" s="225"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="2"/>
@@ -13206,7 +13224,7 @@
       <c r="O52" s="92"/>
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
-      <c r="R52" s="262" t="s">
+      <c r="R52" s="212" t="s">
         <v>64</v>
       </c>
       <c r="S52" s="88"/>
@@ -13216,10 +13234,10 @@
       <c r="W52" s="88"/>
     </row>
     <row r="53" spans="1:23" ht="14.25">
-      <c r="A53" s="210"/>
-      <c r="B53" s="227"/>
-      <c r="C53" s="232"/>
-      <c r="D53" s="253"/>
+      <c r="A53" s="216"/>
+      <c r="B53" s="249"/>
+      <c r="C53" s="231"/>
+      <c r="D53" s="233"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
       <c r="G53" s="34"/>
@@ -13233,7 +13251,7 @@
       <c r="O53" s="92"/>
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
-      <c r="R53" s="262"/>
+      <c r="R53" s="212"/>
       <c r="S53" s="88"/>
       <c r="T53" s="88"/>
       <c r="U53" s="88"/>
@@ -13241,12 +13259,12 @@
       <c r="W53" s="88"/>
     </row>
     <row r="54" spans="1:23" ht="14.25">
-      <c r="A54" s="212" t="s">
+      <c r="A54" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="B54" s="222"/>
-      <c r="C54" s="236"/>
-      <c r="D54" s="236"/>
+      <c r="B54" s="250"/>
+      <c r="C54" s="226"/>
+      <c r="D54" s="226"/>
       <c r="E54" s="71"/>
       <c r="F54" s="72"/>
       <c r="G54" s="73"/>
@@ -13260,7 +13278,7 @@
       <c r="O54" s="147"/>
       <c r="P54" s="148"/>
       <c r="Q54" s="148"/>
-      <c r="R54" s="212" t="s">
+      <c r="R54" s="211" t="s">
         <v>66</v>
       </c>
       <c r="S54" s="88"/>
@@ -13270,10 +13288,10 @@
       <c r="W54" s="88"/>
     </row>
     <row r="55" spans="1:23" ht="14.25">
-      <c r="A55" s="217"/>
-      <c r="B55" s="217"/>
-      <c r="C55" s="211"/>
-      <c r="D55" s="211"/>
+      <c r="A55" s="213"/>
+      <c r="B55" s="213"/>
+      <c r="C55" s="210"/>
+      <c r="D55" s="210"/>
       <c r="E55" s="75"/>
       <c r="F55" s="76"/>
       <c r="G55" s="77"/>
@@ -13287,7 +13305,7 @@
       <c r="O55" s="149"/>
       <c r="P55" s="150"/>
       <c r="Q55" s="150"/>
-      <c r="R55" s="217"/>
+      <c r="R55" s="213"/>
       <c r="S55" s="88"/>
       <c r="T55" s="88"/>
       <c r="U55" s="88"/>
@@ -13295,12 +13313,12 @@
       <c r="W55" s="88"/>
     </row>
     <row r="56" spans="1:23" ht="14.25">
-      <c r="A56" s="210" t="s">
+      <c r="A56" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="220"/>
-      <c r="C56" s="243"/>
-      <c r="D56" s="243"/>
+      <c r="B56" s="251"/>
+      <c r="C56" s="234"/>
+      <c r="D56" s="234"/>
       <c r="E56" s="79"/>
       <c r="F56" s="80"/>
       <c r="G56" s="69"/>
@@ -13314,7 +13332,7 @@
       <c r="O56" s="152"/>
       <c r="P56" s="153"/>
       <c r="Q56" s="3"/>
-      <c r="R56" s="263" t="s">
+      <c r="R56" s="214" t="s">
         <v>68</v>
       </c>
       <c r="S56" s="88"/>
@@ -13324,10 +13342,10 @@
       <c r="W56" s="88"/>
     </row>
     <row r="57" spans="1:23" ht="14.25">
-      <c r="A57" s="217"/>
-      <c r="B57" s="217"/>
-      <c r="C57" s="211"/>
-      <c r="D57" s="233"/>
+      <c r="A57" s="213"/>
+      <c r="B57" s="213"/>
+      <c r="C57" s="210"/>
+      <c r="D57" s="221"/>
       <c r="E57" s="79"/>
       <c r="F57" s="80"/>
       <c r="G57" s="82"/>
@@ -13341,7 +13359,7 @@
       <c r="O57" s="154"/>
       <c r="P57" s="153"/>
       <c r="Q57" s="3"/>
-      <c r="R57" s="211"/>
+      <c r="R57" s="210"/>
       <c r="S57" s="88"/>
       <c r="T57" s="88"/>
       <c r="U57" s="88"/>
@@ -13349,12 +13367,12 @@
       <c r="W57" s="88"/>
     </row>
     <row r="58" spans="1:23" ht="14.25">
-      <c r="A58" s="212" t="s">
+      <c r="A58" s="211" t="s">
         <v>69</v>
       </c>
-      <c r="B58" s="228"/>
-      <c r="C58" s="234"/>
-      <c r="D58" s="234"/>
+      <c r="B58" s="252"/>
+      <c r="C58" s="230"/>
+      <c r="D58" s="230"/>
       <c r="E58" s="13"/>
       <c r="F58" s="84"/>
       <c r="G58" s="14"/>
@@ -13368,7 +13386,7 @@
       <c r="O58" s="156"/>
       <c r="P58" s="157"/>
       <c r="Q58" s="157"/>
-      <c r="R58" s="212" t="s">
+      <c r="R58" s="211" t="s">
         <v>70</v>
       </c>
       <c r="S58" s="88"/>
@@ -13378,10 +13396,10 @@
       <c r="W58" s="88"/>
     </row>
     <row r="59" spans="1:23" ht="14.25">
-      <c r="A59" s="211"/>
-      <c r="B59" s="211"/>
-      <c r="C59" s="211"/>
-      <c r="D59" s="211"/>
+      <c r="A59" s="210"/>
+      <c r="B59" s="210"/>
+      <c r="C59" s="210"/>
+      <c r="D59" s="210"/>
       <c r="E59" s="17"/>
       <c r="F59" s="86"/>
       <c r="G59" s="18"/>
@@ -13395,7 +13413,7 @@
       <c r="O59" s="159"/>
       <c r="P59" s="160"/>
       <c r="Q59" s="160"/>
-      <c r="R59" s="211"/>
+      <c r="R59" s="210"/>
       <c r="S59" s="88"/>
       <c r="T59" s="88"/>
       <c r="U59" s="88"/>
@@ -13403,12 +13421,12 @@
       <c r="W59" s="88"/>
     </row>
     <row r="60" spans="1:23" ht="14.25">
-      <c r="A60" s="210" t="s">
+      <c r="A60" s="216" t="s">
         <v>71</v>
       </c>
-      <c r="B60" s="220"/>
-      <c r="C60" s="244"/>
-      <c r="D60" s="252"/>
+      <c r="B60" s="251"/>
+      <c r="C60" s="235"/>
+      <c r="D60" s="225"/>
       <c r="E60" s="79"/>
       <c r="F60" s="80"/>
       <c r="G60" s="69"/>
@@ -13422,7 +13440,7 @@
       <c r="O60" s="152"/>
       <c r="P60" s="153"/>
       <c r="Q60" s="3"/>
-      <c r="R60" s="263" t="s">
+      <c r="R60" s="214" t="s">
         <v>72</v>
       </c>
       <c r="S60" s="88"/>
@@ -13432,10 +13450,10 @@
       <c r="W60" s="88"/>
     </row>
     <row r="61" spans="1:23" ht="14.25">
-      <c r="A61" s="211"/>
-      <c r="B61" s="217"/>
-      <c r="C61" s="193"/>
-      <c r="D61" s="233"/>
+      <c r="A61" s="210"/>
+      <c r="B61" s="213"/>
+      <c r="C61" s="202"/>
+      <c r="D61" s="221"/>
       <c r="E61" s="79"/>
       <c r="F61" s="80"/>
       <c r="G61" s="82"/>
@@ -13449,7 +13467,7 @@
       <c r="O61" s="154"/>
       <c r="P61" s="153"/>
       <c r="Q61" s="3"/>
-      <c r="R61" s="211"/>
+      <c r="R61" s="210"/>
       <c r="S61" s="88"/>
       <c r="T61" s="88"/>
       <c r="U61" s="88"/>
@@ -13457,12 +13475,12 @@
       <c r="W61" s="88"/>
     </row>
     <row r="62" spans="1:23" ht="14.25">
-      <c r="A62" s="218" t="s">
+      <c r="A62" s="258" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="222"/>
-      <c r="C62" s="245"/>
-      <c r="D62" s="236"/>
+      <c r="B62" s="250"/>
+      <c r="C62" s="236"/>
+      <c r="D62" s="226"/>
       <c r="E62" s="42"/>
       <c r="F62" s="42"/>
       <c r="G62" s="41"/>
@@ -13476,7 +13494,7 @@
       <c r="O62" s="156"/>
       <c r="P62" s="19"/>
       <c r="Q62" s="19"/>
-      <c r="R62" s="212" t="s">
+      <c r="R62" s="211" t="s">
         <v>72</v>
       </c>
       <c r="S62" s="88"/>
@@ -13486,10 +13504,10 @@
       <c r="W62" s="88"/>
     </row>
     <row r="63" spans="1:23" ht="14.25">
-      <c r="A63" s="219"/>
-      <c r="B63" s="211"/>
-      <c r="C63" s="193"/>
-      <c r="D63" s="211"/>
+      <c r="A63" s="259"/>
+      <c r="B63" s="210"/>
+      <c r="C63" s="202"/>
+      <c r="D63" s="210"/>
       <c r="E63" s="15"/>
       <c r="F63" s="15"/>
       <c r="G63" s="24"/>
@@ -13503,7 +13521,7 @@
       <c r="O63" s="106"/>
       <c r="P63" s="15"/>
       <c r="Q63" s="15"/>
-      <c r="R63" s="211"/>
+      <c r="R63" s="210"/>
       <c r="S63" s="88"/>
       <c r="T63" s="88"/>
       <c r="U63" s="88"/>
@@ -17612,50 +17630,104 @@
     </row>
   </sheetData>
   <mergeCells count="166">
-    <mergeCell ref="R48:R49"/>
-    <mergeCell ref="R50:R51"/>
-    <mergeCell ref="R52:R53"/>
-    <mergeCell ref="R54:R55"/>
-    <mergeCell ref="R56:R57"/>
-    <mergeCell ref="R58:R59"/>
-    <mergeCell ref="R60:R61"/>
-    <mergeCell ref="R62:R63"/>
-    <mergeCell ref="R30:R31"/>
-    <mergeCell ref="R32:R33"/>
-    <mergeCell ref="R34:R35"/>
-    <mergeCell ref="R36:R37"/>
-    <mergeCell ref="R38:R39"/>
-    <mergeCell ref="R40:R41"/>
-    <mergeCell ref="R42:R43"/>
-    <mergeCell ref="R44:R45"/>
-    <mergeCell ref="R46:R47"/>
-    <mergeCell ref="R12:R13"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="R24:R25"/>
-    <mergeCell ref="R26:R27"/>
-    <mergeCell ref="R28:R29"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C54:C55"/>
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="C58:C59"/>
     <mergeCell ref="C60:C61"/>
@@ -17680,104 +17752,50 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D38:D39"/>
     <mergeCell ref="D40:D41"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="R12:R13"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="R24:R25"/>
+    <mergeCell ref="R26:R27"/>
+    <mergeCell ref="R28:R29"/>
+    <mergeCell ref="R48:R49"/>
+    <mergeCell ref="R50:R51"/>
+    <mergeCell ref="R52:R53"/>
+    <mergeCell ref="R54:R55"/>
+    <mergeCell ref="R56:R57"/>
+    <mergeCell ref="R58:R59"/>
+    <mergeCell ref="R60:R61"/>
+    <mergeCell ref="R62:R63"/>
+    <mergeCell ref="R30:R31"/>
+    <mergeCell ref="R32:R33"/>
+    <mergeCell ref="R34:R35"/>
+    <mergeCell ref="R36:R37"/>
+    <mergeCell ref="R38:R39"/>
+    <mergeCell ref="R40:R41"/>
+    <mergeCell ref="R42:R43"/>
+    <mergeCell ref="R44:R45"/>
+    <mergeCell ref="R46:R47"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <dataValidations count="7">
